--- a/downloads/shop.xlsx
+++ b/downloads/shop.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hill's Prescription Diet</t>
+          <t>פורינה (חנויות)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -561,24 +561,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>פורינה (חנויות)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>נוסחה: עלות = מחיר ללא מע"מ × (1 − הנחה) × 1.18 ; מחיר ללקוח = עלות × (1 + מרווח %) + מרווח ₪</t>
         </is>
@@ -595,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19096,12 +19080,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Hill's Prescription Diet</t>
+          <t>פורינה (חנויות)</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>חטיף היפואלרגני</t>
+          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -19109,16 +19093,21 @@
           <t>חטיפים</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>12348261</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F350" t="n">
-        <v>24</v>
+        <v>8.18</v>
       </c>
       <c r="G350" t="n">
-        <v>28.32</v>
+        <v>9.65</v>
       </c>
       <c r="H350">
         <f>הגדרות!B8</f>
@@ -19144,12 +19133,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Hill's Prescription Diet</t>
+          <t>פורינה (חנויות)</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>חטיף שמירה על המשקל</t>
+          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -19157,16 +19146,21 @@
           <t>חטיפים</t>
         </is>
       </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>12348037</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F351" t="n">
-        <v>21</v>
+        <v>8.18</v>
       </c>
       <c r="G351" t="n">
-        <v>24.78</v>
+        <v>9.65</v>
       </c>
       <c r="H351">
         <f>הגדרות!B8</f>
@@ -19197,7 +19191,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -19207,7 +19201,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>12348261</t>
+          <t>12364507</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -19222,7 +19216,7 @@
         <v>9.65</v>
       </c>
       <c r="H352">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I352">
@@ -19230,11 +19224,11 @@
         <v/>
       </c>
       <c r="J352">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K352">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L352">
@@ -19250,7 +19244,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
+          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -19260,7 +19254,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>12348037</t>
+          <t>12368621</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -19275,7 +19269,7 @@
         <v>9.65</v>
       </c>
       <c r="H353">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I353">
@@ -19283,11 +19277,11 @@
         <v/>
       </c>
       <c r="J353">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K353">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L353">
@@ -19303,7 +19297,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
+          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -19313,7 +19307,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>12364507</t>
+          <t>12528489</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -19328,7 +19322,7 @@
         <v>9.65</v>
       </c>
       <c r="H354">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I354">
@@ -19336,11 +19330,11 @@
         <v/>
       </c>
       <c r="J354">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K354">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L354">
@@ -19356,7 +19350,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
+          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -19366,7 +19360,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>12368621</t>
+          <t>12280472</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -19381,7 +19375,7 @@
         <v>9.65</v>
       </c>
       <c r="H355">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I355">
@@ -19389,11 +19383,11 @@
         <v/>
       </c>
       <c r="J355">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K355">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L355">
@@ -19409,7 +19403,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
+          <t>פריסקיז פארטי מיקס הודו</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -19419,7 +19413,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>12528489</t>
+          <t>12332654</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -19434,7 +19428,7 @@
         <v>9.65</v>
       </c>
       <c r="H356">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I356">
@@ -19442,11 +19436,11 @@
         <v/>
       </c>
       <c r="J356">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K356">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L356">
@@ -19462,7 +19456,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
+          <t>פריסקיז פארטי מיקס עוף</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -19472,7 +19466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>12280472</t>
+          <t>12332617</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19487,7 +19481,7 @@
         <v>9.65</v>
       </c>
       <c r="H357">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I357">
@@ -19495,11 +19489,11 @@
         <v/>
       </c>
       <c r="J357">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K357">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L357">
@@ -19515,7 +19509,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס הודו</t>
+          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -19525,7 +19519,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>12332654</t>
+          <t>12534203</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19540,7 +19534,7 @@
         <v>9.65</v>
       </c>
       <c r="H358">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I358">
@@ -19548,11 +19542,11 @@
         <v/>
       </c>
       <c r="J358">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K358">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L358">
@@ -19568,7 +19562,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס עוף</t>
+          <t>פריסקיז פלייפולס עוף וכבד</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -19578,7 +19572,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>12332617</t>
+          <t>12534194</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19593,7 +19587,7 @@
         <v>9.65</v>
       </c>
       <c r="H359">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I359">
@@ -19601,11 +19595,11 @@
         <v/>
       </c>
       <c r="J359">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K359">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L359">
@@ -19621,7 +19615,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
+          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -19631,7 +19625,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>12534203</t>
+          <t>12364794</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -19640,13 +19634,13 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>8.18</v>
+        <v>50.67</v>
       </c>
       <c r="G360" t="n">
-        <v>9.65</v>
+        <v>59.79</v>
       </c>
       <c r="H360">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I360">
@@ -19654,11 +19648,11 @@
         <v/>
       </c>
       <c r="J360">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K360">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L360">
@@ -19674,7 +19668,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס עוף וכבד</t>
+          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -19684,7 +19678,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>12534194</t>
+          <t>12349730</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -19693,13 +19687,13 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>8.18</v>
+        <v>50.67</v>
       </c>
       <c r="G361" t="n">
-        <v>9.65</v>
+        <v>59.79</v>
       </c>
       <c r="H361">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I361">
@@ -19707,11 +19701,11 @@
         <v/>
       </c>
       <c r="J361">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K361">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L361">
@@ -19727,7 +19721,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
+          <t>דנטלייף לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -19737,7 +19731,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>12364794</t>
+          <t>12606950</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -19746,13 +19740,13 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>50.67</v>
+        <v>10.2</v>
       </c>
       <c r="G362" t="n">
-        <v>59.79</v>
+        <v>12.04</v>
       </c>
       <c r="H362">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I362">
@@ -19760,11 +19754,11 @@
         <v/>
       </c>
       <c r="J362">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K362">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L362">
@@ -19780,7 +19774,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>דנטלייף לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -19790,7 +19784,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>12349730</t>
+          <t>12606926</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -19799,13 +19793,13 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>50.67</v>
+        <v>10.2</v>
       </c>
       <c r="G363" t="n">
-        <v>59.79</v>
+        <v>12.04</v>
       </c>
       <c r="H363">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I363">
@@ -19813,11 +19807,11 @@
         <v/>
       </c>
       <c r="J363">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K363">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L363">
@@ -19833,7 +19827,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע קטן</t>
+          <t>דנטלייף לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -19843,7 +19837,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>12606950</t>
+          <t>12606948</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -19858,7 +19852,7 @@
         <v>12.04</v>
       </c>
       <c r="H364">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I364">
@@ -19866,11 +19860,11 @@
         <v/>
       </c>
       <c r="J364">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K364">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L364">
@@ -19886,7 +19880,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע בינוני</t>
+          <t>דנטלייף חתול עוף</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -19896,7 +19890,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>12606926</t>
+          <t>12607325</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19905,13 +19899,13 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="G365" t="n">
-        <v>12.04</v>
+        <v>7.67</v>
       </c>
       <c r="H365">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I365">
@@ -19919,11 +19913,11 @@
         <v/>
       </c>
       <c r="J365">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K365">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L365">
@@ -19939,7 +19933,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע גדול</t>
+          <t>דנטלייף חתול סלמון</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -19949,7 +19943,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>12606948</t>
+          <t>12607342</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -19958,13 +19952,13 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="G366" t="n">
-        <v>12.04</v>
+        <v>7.67</v>
       </c>
       <c r="H366">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I366">
@@ -19972,11 +19966,11 @@
         <v/>
       </c>
       <c r="J366">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K366">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L366">
@@ -19992,7 +19986,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>דנטלייף חתול עוף</t>
+          <t>פליקס שלוקים Joyables עוף</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20002,7 +19996,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>12607325</t>
+          <t>12620437</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -20011,13 +20005,13 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>6.5</v>
+        <v>8.49</v>
       </c>
       <c r="G367" t="n">
-        <v>7.67</v>
+        <v>10.02</v>
       </c>
       <c r="H367">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I367">
@@ -20025,11 +20019,11 @@
         <v/>
       </c>
       <c r="J367">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K367">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L367">
@@ -20045,7 +20039,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>דנטלייף חתול סלמון</t>
+          <t>פליקס שלוקים Joyables סלמון</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20055,7 +20049,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>12607342</t>
+          <t>12620438</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -20064,13 +20058,13 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>6.5</v>
+        <v>8.49</v>
       </c>
       <c r="G368" t="n">
-        <v>7.67</v>
+        <v>10.02</v>
       </c>
       <c r="H368">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I368">
@@ -20078,11 +20072,11 @@
         <v/>
       </c>
       <c r="J368">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K368">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L368">
@@ -20098,7 +20092,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables עוף</t>
+          <t>פליקס שלוקים Joyables ברווז</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -20108,7 +20102,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>12620437</t>
+          <t>12620419</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -20123,7 +20117,7 @@
         <v>10.02</v>
       </c>
       <c r="H369">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I369">
@@ -20131,11 +20125,11 @@
         <v/>
       </c>
       <c r="J369">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K369">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L369">
@@ -20151,7 +20145,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables סלמון</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -20161,7 +20155,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>12620438</t>
+          <t>12604543</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -20170,13 +20164,13 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>8.49</v>
+        <v>25.64</v>
       </c>
       <c r="G370" t="n">
-        <v>10.02</v>
+        <v>30.26</v>
       </c>
       <c r="H370">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I370">
@@ -20184,11 +20178,11 @@
         <v/>
       </c>
       <c r="J370">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K370">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L370">
@@ -20204,7 +20198,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables ברווז</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -20214,7 +20208,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>12620419</t>
+          <t>12604772</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -20223,13 +20217,13 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>8.49</v>
+        <v>25.64</v>
       </c>
       <c r="G371" t="n">
-        <v>10.02</v>
+        <v>30.26</v>
       </c>
       <c r="H371">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I371">
@@ -20237,11 +20231,11 @@
         <v/>
       </c>
       <c r="J371">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K371">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L371">
@@ -20257,7 +20251,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -20267,7 +20261,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>12604543</t>
+          <t>12604733</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -20282,7 +20276,7 @@
         <v>30.26</v>
       </c>
       <c r="H372">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I372">
@@ -20290,11 +20284,11 @@
         <v/>
       </c>
       <c r="J372">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K372">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L372">
@@ -20310,7 +20304,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
+          <t>דוגלי אקטיב בקר</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -20320,7 +20314,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>12604772</t>
+          <t>12466720</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -20329,13 +20323,13 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>25.64</v>
+        <v>114.19</v>
       </c>
       <c r="G373" t="n">
-        <v>30.26</v>
+        <v>134.74</v>
       </c>
       <c r="H373">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I373">
@@ -20343,11 +20337,11 @@
         <v/>
       </c>
       <c r="J373">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K373">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L373">
@@ -20363,7 +20357,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
+          <t>דוגלי גורים עוף</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -20373,7 +20367,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>12604733</t>
+          <t>12466622</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -20382,13 +20376,13 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>25.64</v>
+        <v>41.46</v>
       </c>
       <c r="G374" t="n">
-        <v>30.26</v>
+        <v>48.92</v>
       </c>
       <c r="H374">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I374">
@@ -20396,11 +20390,11 @@
         <v/>
       </c>
       <c r="J374">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K374">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L374">
@@ -20416,7 +20410,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>דוגלי אקטיב בקר</t>
+          <t>דוגלי גזע קטן בקר</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -20426,7 +20420,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>12466720</t>
+          <t>12613172</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -20435,13 +20429,13 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>114.19</v>
+        <v>39.49</v>
       </c>
       <c r="G375" t="n">
-        <v>134.74</v>
+        <v>46.6</v>
       </c>
       <c r="H375">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I375">
@@ -20449,11 +20443,11 @@
         <v/>
       </c>
       <c r="J375">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K375">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L375">
@@ -20469,7 +20463,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>דוגלי גורים עוף</t>
+          <t>דוגלי בוגר עוף</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -20479,7 +20473,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>12466622</t>
+          <t>12368765</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -20488,13 +20482,13 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>41.46</v>
+        <v>37.61</v>
       </c>
       <c r="G376" t="n">
-        <v>48.92</v>
+        <v>44.38</v>
       </c>
       <c r="H376">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I376">
@@ -20502,11 +20496,11 @@
         <v/>
       </c>
       <c r="J376">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K376">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L376">
@@ -20522,7 +20516,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>דוגלי גזע קטן בקר</t>
+          <t>דוגלי בוגר בקר</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -20532,7 +20526,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>12613172</t>
+          <t>12368766</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -20541,13 +20535,13 @@
         </is>
       </c>
       <c r="F377" t="n">
-        <v>39.49</v>
+        <v>37.61</v>
       </c>
       <c r="G377" t="n">
-        <v>46.6</v>
+        <v>44.38</v>
       </c>
       <c r="H377">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I377">
@@ -20555,11 +20549,11 @@
         <v/>
       </c>
       <c r="J377">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K377">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L377">
@@ -20585,7 +20579,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>12368765</t>
+          <t>12368676</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -20594,13 +20588,13 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>37.61</v>
+        <v>108.76</v>
       </c>
       <c r="G378" t="n">
-        <v>44.38</v>
+        <v>128.34</v>
       </c>
       <c r="H378">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I378">
@@ -20608,11 +20602,11 @@
         <v/>
       </c>
       <c r="J378">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K378">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L378">
@@ -20638,7 +20632,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>12368766</t>
+          <t>12368675</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -20647,13 +20641,13 @@
         </is>
       </c>
       <c r="F379" t="n">
-        <v>37.61</v>
+        <v>108.76</v>
       </c>
       <c r="G379" t="n">
-        <v>44.38</v>
+        <v>128.34</v>
       </c>
       <c r="H379">
-        <f>הגדרות!B9</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I379">
@@ -20661,121 +20655,15 @@
         <v/>
       </c>
       <c r="J379">
-        <f>הגדרות!C9</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K379">
-        <f>הגדרות!D9</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L379">
         <f>I379*(1+J379/100)+K379</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>פורינה (חנויות)</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>דוגלי בוגר עוף</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>חטיפים</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>12368676</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F380" t="n">
-        <v>108.76</v>
-      </c>
-      <c r="G380" t="n">
-        <v>128.34</v>
-      </c>
-      <c r="H380">
-        <f>הגדרות!B9</f>
-        <v/>
-      </c>
-      <c r="I380">
-        <f>F380*(1-H380/100)*1.18</f>
-        <v/>
-      </c>
-      <c r="J380">
-        <f>הגדרות!C9</f>
-        <v/>
-      </c>
-      <c r="K380">
-        <f>הגדרות!D9</f>
-        <v/>
-      </c>
-      <c r="L380">
-        <f>I380*(1+J380/100)+K380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>פורינה (חנויות)</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>דוגלי בוגר בקר</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>חטיפים</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>12368675</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F381" t="n">
-        <v>108.76</v>
-      </c>
-      <c r="G381" t="n">
-        <v>128.34</v>
-      </c>
-      <c r="H381">
-        <f>הגדרות!B9</f>
-        <v/>
-      </c>
-      <c r="I381">
-        <f>F381*(1-H381/100)*1.18</f>
-        <v/>
-      </c>
-      <c r="J381">
-        <f>הגדרות!C9</f>
-        <v/>
-      </c>
-      <c r="K381">
-        <f>הגדרות!D9</f>
-        <v/>
-      </c>
-      <c r="L381">
-        <f>I381*(1+J381/100)+K381</f>
         <v/>
       </c>
     </row>

--- a/downloads/shop.xlsx
+++ b/downloads/shop.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L379"/>
+  <dimension ref="A1:L376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>חטיף הילס היפואלרגני לכלב 200 גרם</t>
+          <t>תוסף מפרקים  DASUQUIN Nutramax חטיפים לכלב בינוני/קטן, 84 יח'</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>40608557</t>
+          <t>181525</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -15765,10 +15765,10 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="G287" t="n">
-        <v>27.14</v>
+        <v>184.08</v>
       </c>
       <c r="H287">
         <f>הגדרות!B5</f>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>חטיף פודיס נגיסי סלמון 100 גרם</t>
+          <t>תוסף מפרקים  DASUQUIN Nutramax חטיפים לכלב גדול, 84 יח'</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>48000004</t>
+          <t>181526</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="G288" t="n">
-        <v>7.08</v>
+        <v>224.2</v>
       </c>
       <c r="H288">
         <f>הגדרות!B5</f>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>חטיף פודיס רצועות עוף רכות 100 גרם</t>
+          <t>חטיף FOODIES רצועות עוף רכות, 100 גרם</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>חטיף פודיס נתחי ברווז רכים 100 גרם</t>
+          <t>חטיף FOODIES נגיסי סלמון, 100 גרם</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>48000001</t>
+          <t>48000004</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15924,10 +15924,10 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="G290" t="n">
-        <v>5.07</v>
+        <v>7.08</v>
       </c>
       <c r="H290">
         <f>הגדרות!B5</f>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>חטיף פודיס נגיסי ברווז 100 גרם</t>
+          <t>חטיף FOODIES נגיסי ברווז, 100 גרם</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16011,17 +16011,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Kit4Cat חול</t>
+          <t>חטיף FOODIES גלילת ברווז עם עצם דנטלית 100 גרם</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>460001</t>
+          <t>48000013</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16030,10 +16030,10 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G292" t="n">
-        <v>41.3</v>
+        <v>7.08</v>
       </c>
       <c r="H292">
         <f>הגדרות!B5</f>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>תוסף מפרקים  DASUQUIN Nutramax חטיפים לכלב בינוני/קטן, 84 יח'</t>
+          <t>חטיף FOODIES גלילת כבש, אורז ועור בקר, 100 גרם</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>181525</t>
+          <t>48000015</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16083,10 +16083,10 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="G293" t="n">
-        <v>184.08</v>
+        <v>7.08</v>
       </c>
       <c r="H293">
         <f>הגדרות!B5</f>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>תוסף מפרקים  DASUQUIN Nutramax חטיפים לכלב גדול, 84 יח'</t>
+          <t>חטיף FOODIES מקלות לעיסה עוף ועור בקר 1 ק"ג</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>181526</t>
+          <t>48000025</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16136,10 +16136,10 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="G294" t="n">
-        <v>224.2</v>
+        <v>62.54</v>
       </c>
       <c r="H294">
         <f>הגדרות!B5</f>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>חטיף FOODIES גלילת ברווז עם עצם דנטלית 100 גרם</t>
+          <t>חטיף FOODIES גלילת עוף ועור בקר ג'מבו 1 ק"ג</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>48000013</t>
+          <t>48000027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16189,10 +16189,10 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="G295" t="n">
-        <v>7.08</v>
+        <v>62.54</v>
       </c>
       <c r="H295">
         <f>הגדרות!B5</f>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>חטיף FOODIES גלילת כבש, אורז ועור בקר, 100 גרם</t>
+          <t>חטיף FOODIES גלילת ברווז עם עצם סידן 1 ק"ג</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>48000015</t>
+          <t>48000028</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -16242,10 +16242,10 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="G296" t="n">
-        <v>7.08</v>
+        <v>62.54</v>
       </c>
       <c r="H296">
         <f>הגדרות!B5</f>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>חטיף FOODIES מקלות לעיסה עוף ועור בקר 1 ק"ג</t>
+          <t>חטיף FOODIES פילה חזה עוף 1 ק"ג</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>48000025</t>
+          <t>48000029</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>חטיף FOODIES גלילת עוף ועור בקר ג'מבו 1 ק"ג</t>
+          <t>ק"ג 1 חטיף פודיס ברווז על מקלוני עור בקר,</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>48000027</t>
+          <t>48000030</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>חטיף FOODIES גלילת ברווז עם עצם סידן 1 ק"ג</t>
+          <t>חטיף FOODIES גלילת כבש ועור בקר, 1 ק"ג</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>48000028</t>
+          <t>48000031</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>חטיף FOODIES פילה חזה עוף 1 ק"ג</t>
+          <t>ק"ג 1 חטיף פודיס מקלות לעיסה כבש ועור בקר,</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>48000029</t>
+          <t>48000032</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ק"ג 1 חטיף פודיס ברווז על מקלוני עור בקר,</t>
+          <t>חטיף FOODIES מקלות לעיסה סלמון ועור בקר, 1 ק"ג</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>48000030</t>
+          <t>48000033</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16536,37 +16536,37 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>וטמרקט</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>חטיף FOODIES גלילת כבש ועור בקר, 1 ק"ג</t>
+          <t>@ סדיניה 35 60X90 יח' TENA BED @</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>48000031</t>
+          <t>33262-1</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F302" t="n">
-        <v>53</v>
+        <v>31.36</v>
       </c>
       <c r="G302" t="n">
-        <v>62.54</v>
+        <v>37</v>
       </c>
       <c r="H302">
-        <f>הגדרות!B5</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I302">
@@ -16574,11 +16574,11 @@
         <v/>
       </c>
       <c r="J302">
-        <f>הגדרות!C5</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K302">
-        <f>הגדרות!D5</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L302">
@@ -16589,37 +16589,37 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>וטמרקט</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ק"ג 1 חטיף פודיס מקלות לעיסה כבש ועור בקר,</t>
+          <t>ANTIGONE WIPES 19*20 500</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>48000032</t>
+          <t>M0002020</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F303" t="n">
-        <v>53</v>
+        <v>71.42</v>
       </c>
       <c r="G303" t="n">
-        <v>62.54</v>
+        <v>84.27</v>
       </c>
       <c r="H303">
-        <f>הגדרות!B5</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I303">
@@ -16627,11 +16627,11 @@
         <v/>
       </c>
       <c r="J303">
-        <f>הגדרות!C5</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K303">
-        <f>הגדרות!D5</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L303">
@@ -16642,37 +16642,37 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>וטמרקט</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>חטיף FOODIES מקלות לעיסה סלמון ועור בקר, 1 ק"ג</t>
+          <t>ANTIGONE WIPES 20*20 200</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>48000033</t>
+          <t>100003</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F304" t="n">
-        <v>53</v>
+        <v>30.32</v>
       </c>
       <c r="G304" t="n">
-        <v>62.54</v>
+        <v>35.78</v>
       </c>
       <c r="H304">
-        <f>הגדרות!B5</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I304">
@@ -16680,11 +16680,11 @@
         <v/>
       </c>
       <c r="J304">
-        <f>הגדרות!C5</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K304">
-        <f>הגדרות!D5</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L304">
@@ -16700,17 +16700,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>@ סדיניה 35 60X90 יח' TENA BED @</t>
+          <t>CETRIN 1 LITTER SOL</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>33262-1</t>
+          <t>33365</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -16719,10 +16719,10 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>31.36</v>
+        <v>30.84</v>
       </c>
       <c r="G305" t="n">
-        <v>37</v>
+        <v>36.39</v>
       </c>
       <c r="H305">
         <f>הגדרות!B6</f>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ANTIGONE WIPES 19*20 500</t>
+          <t>DOUXO S3 CALM MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>M0002020</t>
+          <t>81-105</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>71.42</v>
+        <v>58.47</v>
       </c>
       <c r="G306" t="n">
-        <v>84.27</v>
+        <v>69</v>
       </c>
       <c r="H306">
         <f>הגדרות!B6</f>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ANTIGONE WIPES 20*20 200</t>
+          <t>DOUXO S3 PYO MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>100003</t>
+          <t>81-101</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16825,10 +16825,10 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>30.32</v>
+        <v>58.47</v>
       </c>
       <c r="G307" t="n">
-        <v>35.78</v>
+        <v>69</v>
       </c>
       <c r="H307">
         <f>הגדרות!B6</f>
@@ -16859,17 +16859,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>CETRIN 1 LITTER SOL</t>
+          <t>DOUXO S3 PYO PADS</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>81-107</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16878,10 +16878,10 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>30.84</v>
+        <v>36.44</v>
       </c>
       <c r="G308" t="n">
-        <v>36.39</v>
+        <v>43</v>
       </c>
       <c r="H308">
         <f>הגדרות!B6</f>
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DOUXO S3 CALM MOUSSE 150 ML</t>
+          <t>DOUXO S3 SEB MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>81-105</t>
+          <t>81-103</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16965,17 +16965,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DOUXO S3 PYO MOUSSE 150 ML</t>
+          <t>Easy Go 500 Litter - איזי גו</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>81-101</t>
+          <t>18033-1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16984,10 +16984,10 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>58.47</v>
+        <v>14.32</v>
       </c>
       <c r="G310" t="n">
-        <v>69</v>
+        <v>16.9</v>
       </c>
       <c r="H310">
         <f>הגדרות!B6</f>
@@ -17018,17 +17018,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DOUXO S3 PYO PADS</t>
+          <t>Pinchers 45chews peanut butter pill hiding treat</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>81-107</t>
+          <t>090062J.045</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17037,10 +17037,10 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>36.44</v>
+        <v>22.3</v>
       </c>
       <c r="G311" t="n">
-        <v>43</v>
+        <v>26.31</v>
       </c>
       <c r="H311">
         <f>הגדרות!B6</f>
@@ -17071,17 +17071,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DOUXO S3 SEB MOUSSE 150 ML</t>
+          <t>אלונקה רכה מתקפלת NAR QuikLitter</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>81-103</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>58.47</v>
+        <v>194.49</v>
       </c>
       <c r="G312" t="n">
-        <v>69</v>
+        <v>229.5</v>
       </c>
       <c r="H312">
         <f>הגדרות!B6</f>
@@ -17124,17 +17124,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Easy Go 500 Litter - איזי גו</t>
+          <t>כלוב נשיאה אטלס 10 ללא מזרון Ferplast</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>18033-1</t>
+          <t>5550279</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17143,10 +17143,10 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>14.32</v>
+        <v>50.85</v>
       </c>
       <c r="G313" t="n">
-        <v>16.9</v>
+        <v>60</v>
       </c>
       <c r="H313">
         <f>הגדרות!B6</f>
@@ -17177,17 +17177,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Pinchers 45chews peanut butter pill hiding treat</t>
+          <t>כלוב נשיאה אטלס 20 ללא מזרון Ferplast</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>090062J.045</t>
+          <t>5550280</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -17196,10 +17196,10 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>22.3</v>
+        <v>88.14</v>
       </c>
       <c r="G314" t="n">
-        <v>26.31</v>
+        <v>104</v>
       </c>
       <c r="H314">
         <f>הגדרות!B6</f>
@@ -17230,17 +17230,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>אלונקה רכה מתקפלת NAR QuikLitter</t>
+          <t>מברשת רחצת ידיים לפני ניתוח, סטר', מדיקפרו</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>194.49</v>
+        <v>0.87</v>
       </c>
       <c r="G315" t="n">
-        <v>229.5</v>
+        <v>1.03</v>
       </c>
       <c r="H315">
         <f>הגדרות!B6</f>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>כלוב נשיאה אטלס 10 ללא מזרון Ferplast</t>
+          <t>מגבונים - Clinell sporicidal wipesn 1/6</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>5550279</t>
+          <t>CS25</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -17302,10 +17302,10 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>50.85</v>
+        <v>156.78</v>
       </c>
       <c r="G316" t="n">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="H316">
         <f>הגדרות!B6</f>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>כלוב נשיאה אטלס 20 ללא מזרון Ferplast</t>
+          <t>מגבונים - Clinell Universal wipes clip pack 50</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>5550280</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>88.14</v>
+        <v>9.25</v>
       </c>
       <c r="G317" t="n">
-        <v>104</v>
+        <v>10.92</v>
       </c>
       <c r="H317">
         <f>הגדרות!B6</f>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>מברשת רחצת ידיים לפני ניתוח, סטר', מדיקפרו</t>
+          <t>מגבונים - Clinell Universal Wipes pack of 200</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>0.87</v>
+        <v>19.92</v>
       </c>
       <c r="G318" t="n">
-        <v>1.03</v>
+        <v>23.5</v>
       </c>
       <c r="H318">
         <f>הגדרות!B6</f>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell sporicidal wipesn 1/6</t>
+          <t>מגבונים מדי-קלין אקסטרה עבים מועשר באלוורה 500 יח 20X16 ס"מ</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -17452,7 +17452,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>CS25</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -17461,10 +17461,10 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>156.78</v>
+        <v>22.88</v>
       </c>
       <c r="G319" t="n">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H319">
         <f>הגדרות!B6</f>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell Universal wipes clip pack 50</t>
+          <t>מגבונים מדי-קלין מועשרים באלוורה 500 יח' 28X20 ס"מ</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>9.25</v>
+        <v>22.88</v>
       </c>
       <c r="G320" t="n">
-        <v>10.92</v>
+        <v>27</v>
       </c>
       <c r="H320">
         <f>הגדרות!B6</f>
@@ -17548,17 +17548,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell Universal Wipes pack of 200</t>
+          <t>מיטה חשמלית דגם GUESS 402 מעקה מגלוון</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>883135</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -17567,10 +17567,10 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>19.92</v>
+        <v>6288.14</v>
       </c>
       <c r="G321" t="n">
-        <v>23.5</v>
+        <v>7420</v>
       </c>
       <c r="H321">
         <f>הגדרות!B6</f>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>מגבונים מדי-קלין אקסטרה עבים מועשר באלוורה 500 יח 20X16 ס"מ</t>
+          <t>מספריים אל חלד לציפורניים REISZ</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>434457</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>22.88</v>
+        <v>21.17</v>
       </c>
       <c r="G322" t="n">
-        <v>27</v>
+        <v>24.98</v>
       </c>
       <c r="H322">
         <f>הגדרות!B6</f>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>מגבונים מדי-קלין מועשרים באלוורה 500 יח' 28X20 ס"מ</t>
+          <t>משושת ג'ל 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>128695</t>
+          <t>67-105</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -17673,10 +17673,10 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>22.88</v>
+        <v>157.63</v>
       </c>
       <c r="G323" t="n">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="H323">
         <f>הגדרות!B6</f>
@@ -17707,17 +17707,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>מיטה חשמלית דגם GUESS 402 מעקה מגלוון</t>
+          <t>משושת קרם 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>883135</t>
+          <t>67-103</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>6288.14</v>
+        <v>157.63</v>
       </c>
       <c r="G324" t="n">
-        <v>7420</v>
+        <v>186</v>
       </c>
       <c r="H324">
         <f>הגדרות!B6</f>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>מספריים אל חלד לציפורניים REISZ</t>
+          <t>נייר לניגוב עדשות מיקרוסקופ 1159 1/280 Kimwipes</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>434457</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -17779,10 +17779,10 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>21.17</v>
+        <v>26.44</v>
       </c>
       <c r="G325" t="n">
-        <v>24.98</v>
+        <v>31.2</v>
       </c>
       <c r="H325">
         <f>הגדרות!B6</f>
@@ -17813,17 +17813,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>משושת ג'ל 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
+          <t>סיר לילה פלסטיק/ מיטה גדול עם ידית, מדיקפרו</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>67-105</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -17832,10 +17832,10 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>157.63</v>
+        <v>11.86</v>
       </c>
       <c r="G326" t="n">
-        <v>186</v>
+        <v>14</v>
       </c>
       <c r="H326">
         <f>הגדרות!B6</f>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>משושת קרם 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
+          <t>קוצץ ציפורניים, מדיקפרו</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>67-103</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -17885,10 +17885,10 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>157.63</v>
+        <v>3.32</v>
       </c>
       <c r="G327" t="n">
-        <v>186</v>
+        <v>3.92</v>
       </c>
       <c r="H327">
         <f>הגדרות!B6</f>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>נייר לניגוב עדשות מיקרוסקופ 1159 1/280 Kimwipes</t>
+          <t>ראש למכונת תספורת (סכין) 40 - 0.25 מ"מ LAUBE</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17938,10 +17938,10 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>26.44</v>
+        <v>120.13</v>
       </c>
       <c r="G328" t="n">
-        <v>31.2</v>
+        <v>141.75</v>
       </c>
       <c r="H328">
         <f>הגדרות!B6</f>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>סיר לילה פלסטיק/ מיטה גדול עם ידית, מדיקפרו</t>
+          <t>רצועה ללוח גב צבע כתום עם אבזם מתכת</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -17991,10 +17991,10 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>11.86</v>
+        <v>71.19</v>
       </c>
       <c r="G329" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="H329">
         <f>הגדרות!B6</f>
@@ -18025,17 +18025,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>קוצץ ציפורניים, מדיקפרו</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי L</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18044,10 +18044,10 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3.32</v>
+        <v>5.91</v>
       </c>
       <c r="G330" t="n">
-        <v>3.92</v>
+        <v>6.97</v>
       </c>
       <c r="H330">
         <f>הגדרות!B6</f>
@@ -18078,17 +18078,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ראש למכונת תספורת (סכין) 40 - 0.25 מ"מ LAUBE</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי M</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18097,10 +18097,10 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>120.13</v>
+        <v>6.19</v>
       </c>
       <c r="G331" t="n">
-        <v>141.75</v>
+        <v>7.3</v>
       </c>
       <c r="H331">
         <f>הגדרות!B6</f>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>רצועה ללוח גב צבע כתום עם אבזם מתכת</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי XL</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -18150,10 +18150,10 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>71.19</v>
+        <v>6.36</v>
       </c>
       <c r="G332" t="n">
-        <v>84</v>
+        <v>7.5</v>
       </c>
       <c r="H332">
         <f>הגדרות!B6</f>
@@ -18179,37 +18179,37 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי L</t>
+          <t>Keto Tris Finger Wipes 50 units</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>DERMA-SP1330</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>5.91</v>
+        <v>59</v>
       </c>
       <c r="G333" t="n">
-        <v>6.97</v>
+        <v>69.62</v>
       </c>
       <c r="H333">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I333">
@@ -18217,11 +18217,11 @@
         <v/>
       </c>
       <c r="J333">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K333">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L333">
@@ -18232,37 +18232,37 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי M</t>
+          <t>Tris Ophto Wipes 50ct</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>DZOO-TWX</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>6.19</v>
+        <v>58</v>
       </c>
       <c r="G334" t="n">
-        <v>7.3</v>
+        <v>68.44</v>
       </c>
       <c r="H334">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I334">
@@ -18270,11 +18270,11 @@
         <v/>
       </c>
       <c r="J334">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K334">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L334">
@@ -18285,37 +18285,37 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי XL</t>
+          <t>Pill Splitter</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>FIONA-821070-1</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>6.36</v>
+        <v>7</v>
       </c>
       <c r="G335" t="n">
-        <v>7.5</v>
+        <v>8.26</v>
       </c>
       <c r="H335">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I335">
@@ -18323,11 +18323,11 @@
         <v/>
       </c>
       <c r="J335">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K335">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L335">
@@ -18343,17 +18343,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Keto Tris Finger Wipes 50 units</t>
+          <t>Calming Spray 200ml</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DERMA-SP1330</t>
+          <t>PR-79583</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -18362,10 +18362,10 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G336" t="n">
-        <v>69.62</v>
+        <v>54.28</v>
       </c>
       <c r="H336">
         <f>הגדרות!B7</f>
@@ -18396,17 +18396,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tris Ophto Wipes 50ct</t>
+          <t>Mini Calming Spray 15ml</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DZOO-TWX</t>
+          <t>PR-79664</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -18415,10 +18415,10 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G337" t="n">
-        <v>68.44</v>
+        <v>21.24</v>
       </c>
       <c r="H337">
         <f>הגדרות!B7</f>
@@ -18449,17 +18449,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Pill Splitter</t>
+          <t>Battery Atomizer Refill 300ml</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>FIONA-821070-1</t>
+          <t>PR-79744</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -18468,10 +18468,10 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="G338" t="n">
-        <v>8.26</v>
+        <v>66.08</v>
       </c>
       <c r="H338">
         <f>הגדרות!B7</f>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Calming Spray 200ml</t>
+          <t>Battery Atomizer</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>PR-79583</t>
+          <t>PR-79745</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -18521,10 +18521,10 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>46</v>
+        <v>185</v>
       </c>
       <c r="G339" t="n">
-        <v>54.28</v>
+        <v>218.3</v>
       </c>
       <c r="H339">
         <f>הגדרות!B7</f>
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mini Calming Spray 15ml</t>
+          <t>Calming Wipe Sachet (12)</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>PR-79664</t>
+          <t>PR-79881</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -18608,17 +18608,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Battery Atomizer Refill 300ml</t>
+          <t>Boredom Buster forager kit</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>צעצועים</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>PR-79744</t>
+          <t>PR-80128</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -18627,10 +18627,10 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="G341" t="n">
-        <v>66.08</v>
+        <v>123.9</v>
       </c>
       <c r="H341">
         <f>הגדרות!B7</f>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Battery Atomizer</t>
+          <t>Calming Bandana Kit EXTRA SMALL</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>PR-79745</t>
+          <t>PR-79959</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -18680,10 +18680,10 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="G342" t="n">
-        <v>218.3</v>
+        <v>51.92</v>
       </c>
       <c r="H342">
         <f>הגדרות!B7</f>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Calming Wipe Sachet (12)</t>
+          <t>Calming Bandana Kit SMALL</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>PR-79881</t>
+          <t>PR-79960</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -18733,10 +18733,10 @@
         </is>
       </c>
       <c r="F343" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G343" t="n">
-        <v>21.24</v>
+        <v>51.92</v>
       </c>
       <c r="H343">
         <f>הגדרות!B7</f>
@@ -18767,17 +18767,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Boredom Buster forager kit</t>
+          <t>Calming Bandana Kit MEDIUM</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>צעצועים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>PR-80128</t>
+          <t>PR-79961</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="F344" t="n">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="G344" t="n">
-        <v>123.9</v>
+        <v>51.92</v>
       </c>
       <c r="H344">
         <f>הגדרות!B7</f>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit EXTRA SMALL</t>
+          <t>Calming Bandana Kit LARGE</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>PR-79959</t>
+          <t>PR-79962</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit SMALL</t>
+          <t>Calming Spray 400ml – PROF. PACK</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>PR-79960</t>
+          <t>PR-79983</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -18892,10 +18892,10 @@
         </is>
       </c>
       <c r="F346" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G346" t="n">
-        <v>51.92</v>
+        <v>71.98</v>
       </c>
       <c r="H346">
         <f>הגדרות!B7</f>
@@ -18921,37 +18921,37 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>פורינה (חנויות)</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit MEDIUM</t>
+          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>PR-79961</t>
+          <t>12348261</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F347" t="n">
-        <v>44</v>
+        <v>8.18</v>
       </c>
       <c r="G347" t="n">
-        <v>51.92</v>
+        <v>9.65</v>
       </c>
       <c r="H347">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I347">
@@ -18959,11 +18959,11 @@
         <v/>
       </c>
       <c r="J347">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K347">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L347">
@@ -18974,37 +18974,37 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>פורינה (חנויות)</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit LARGE</t>
+          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>PR-79962</t>
+          <t>12348037</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F348" t="n">
-        <v>44</v>
+        <v>8.18</v>
       </c>
       <c r="G348" t="n">
-        <v>51.92</v>
+        <v>9.65</v>
       </c>
       <c r="H348">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I348">
@@ -19012,11 +19012,11 @@
         <v/>
       </c>
       <c r="J348">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K348">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L348">
@@ -19027,37 +19027,37 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>פורינה (חנויות)</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Calming Spray 400ml – PROF. PACK</t>
+          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>PR-79983</t>
+          <t>12364507</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F349" t="n">
-        <v>61</v>
+        <v>8.18</v>
       </c>
       <c r="G349" t="n">
-        <v>71.98</v>
+        <v>9.65</v>
       </c>
       <c r="H349">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B8</f>
         <v/>
       </c>
       <c r="I349">
@@ -19065,11 +19065,11 @@
         <v/>
       </c>
       <c r="J349">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C8</f>
         <v/>
       </c>
       <c r="K349">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D8</f>
         <v/>
       </c>
       <c r="L349">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>12348261</t>
+          <t>12368621</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
+          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>12348037</t>
+          <t>12528489</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
+          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>12364507</t>
+          <t>12280472</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
+          <t>פריסקיז פארטי מיקס הודו</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>12368621</t>
+          <t>12332654</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
+          <t>פריסקיז פארטי מיקס עוף</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>12528489</t>
+          <t>12332617</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
+          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>12280472</t>
+          <t>12534203</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס הודו</t>
+          <t>פריסקיז פלייפולס עוף וכבד</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>12332654</t>
+          <t>12534194</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס עוף</t>
+          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>12332617</t>
+          <t>12364794</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>8.18</v>
+        <v>50.67</v>
       </c>
       <c r="G357" t="n">
-        <v>9.65</v>
+        <v>59.79</v>
       </c>
       <c r="H357">
         <f>הגדרות!B8</f>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
+          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>12534203</t>
+          <t>12349730</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19528,10 +19528,10 @@
         </is>
       </c>
       <c r="F358" t="n">
-        <v>8.18</v>
+        <v>50.67</v>
       </c>
       <c r="G358" t="n">
-        <v>9.65</v>
+        <v>59.79</v>
       </c>
       <c r="H358">
         <f>הגדרות!B8</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס עוף וכבד</t>
+          <t>דנטלייף לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>12534194</t>
+          <t>12606950</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19581,10 +19581,10 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>8.18</v>
+        <v>10.2</v>
       </c>
       <c r="G359" t="n">
-        <v>9.65</v>
+        <v>12.04</v>
       </c>
       <c r="H359">
         <f>הגדרות!B8</f>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
+          <t>דנטלייף לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>12364794</t>
+          <t>12606926</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -19634,10 +19634,10 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>50.67</v>
+        <v>10.2</v>
       </c>
       <c r="G360" t="n">
-        <v>59.79</v>
+        <v>12.04</v>
       </c>
       <c r="H360">
         <f>הגדרות!B8</f>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>דנטלייף לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>12349730</t>
+          <t>12606948</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>50.67</v>
+        <v>10.2</v>
       </c>
       <c r="G361" t="n">
-        <v>59.79</v>
+        <v>12.04</v>
       </c>
       <c r="H361">
         <f>הגדרות!B8</f>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע קטן</t>
+          <t>דנטלייף חתול עוף</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>12606950</t>
+          <t>12607325</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -19740,10 +19740,10 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="G362" t="n">
-        <v>12.04</v>
+        <v>7.67</v>
       </c>
       <c r="H362">
         <f>הגדרות!B8</f>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע בינוני</t>
+          <t>דנטלייף חתול סלמון</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>12606926</t>
+          <t>12607342</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -19793,10 +19793,10 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="G363" t="n">
-        <v>12.04</v>
+        <v>7.67</v>
       </c>
       <c r="H363">
         <f>הגדרות!B8</f>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע גדול</t>
+          <t>פליקס שלוקים Joyables עוף</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>12606948</t>
+          <t>12620437</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -19846,10 +19846,10 @@
         </is>
       </c>
       <c r="F364" t="n">
-        <v>10.2</v>
+        <v>8.49</v>
       </c>
       <c r="G364" t="n">
-        <v>12.04</v>
+        <v>10.02</v>
       </c>
       <c r="H364">
         <f>הגדרות!B8</f>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>דנטלייף חתול עוף</t>
+          <t>פליקס שלוקים Joyables סלמון</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>12607325</t>
+          <t>12620438</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19899,10 +19899,10 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>6.5</v>
+        <v>8.49</v>
       </c>
       <c r="G365" t="n">
-        <v>7.67</v>
+        <v>10.02</v>
       </c>
       <c r="H365">
         <f>הגדרות!B8</f>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>דנטלייף חתול סלמון</t>
+          <t>פליקס שלוקים Joyables ברווז</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>12607342</t>
+          <t>12620419</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>6.5</v>
+        <v>8.49</v>
       </c>
       <c r="G366" t="n">
-        <v>7.67</v>
+        <v>10.02</v>
       </c>
       <c r="H366">
         <f>הגדרות!B8</f>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables עוף</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>12620437</t>
+          <t>12604543</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -20005,10 +20005,10 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>8.49</v>
+        <v>25.64</v>
       </c>
       <c r="G367" t="n">
-        <v>10.02</v>
+        <v>30.26</v>
       </c>
       <c r="H367">
         <f>הגדרות!B8</f>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables סלמון</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>12620438</t>
+          <t>12604772</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -20058,10 +20058,10 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>8.49</v>
+        <v>25.64</v>
       </c>
       <c r="G368" t="n">
-        <v>10.02</v>
+        <v>30.26</v>
       </c>
       <c r="H368">
         <f>הגדרות!B8</f>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables ברווז</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>12620419</t>
+          <t>12604733</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -20111,10 +20111,10 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>8.49</v>
+        <v>25.64</v>
       </c>
       <c r="G369" t="n">
-        <v>10.02</v>
+        <v>30.26</v>
       </c>
       <c r="H369">
         <f>הגדרות!B8</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
+          <t>דוגלי אקטיב בקר</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>12604543</t>
+          <t>12466720</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>25.64</v>
+        <v>114.19</v>
       </c>
       <c r="G370" t="n">
-        <v>30.26</v>
+        <v>134.74</v>
       </c>
       <c r="H370">
         <f>הגדרות!B8</f>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
+          <t>דוגלי גורים עוף</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>12604772</t>
+          <t>12466622</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -20217,10 +20217,10 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>25.64</v>
+        <v>41.46</v>
       </c>
       <c r="G371" t="n">
-        <v>30.26</v>
+        <v>48.92</v>
       </c>
       <c r="H371">
         <f>הגדרות!B8</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
+          <t>דוגלי גזע קטן בקר</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>12604733</t>
+          <t>12613172</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -20270,10 +20270,10 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>25.64</v>
+        <v>39.49</v>
       </c>
       <c r="G372" t="n">
-        <v>30.26</v>
+        <v>46.6</v>
       </c>
       <c r="H372">
         <f>הגדרות!B8</f>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>דוגלי אקטיב בקר</t>
+          <t>דוגלי בוגר עוף</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>12466720</t>
+          <t>12368765</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>114.19</v>
+        <v>37.61</v>
       </c>
       <c r="G373" t="n">
-        <v>134.74</v>
+        <v>44.38</v>
       </c>
       <c r="H373">
         <f>הגדרות!B8</f>
@@ -20357,7 +20357,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>דוגלי גורים עוף</t>
+          <t>דוגלי בוגר בקר</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>12466622</t>
+          <t>12368766</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -20376,10 +20376,10 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>41.46</v>
+        <v>37.61</v>
       </c>
       <c r="G374" t="n">
-        <v>48.92</v>
+        <v>44.38</v>
       </c>
       <c r="H374">
         <f>הגדרות!B8</f>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>דוגלי גזע קטן בקר</t>
+          <t>דוגלי בוגר עוף</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>12613172</t>
+          <t>12368676</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>39.49</v>
+        <v>108.76</v>
       </c>
       <c r="G375" t="n">
-        <v>46.6</v>
+        <v>128.34</v>
       </c>
       <c r="H375">
         <f>הגדרות!B8</f>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>דוגלי בוגר עוף</t>
+          <t>דוגלי בוגר בקר</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>12368765</t>
+          <t>12368675</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -20482,10 +20482,10 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>37.61</v>
+        <v>108.76</v>
       </c>
       <c r="G376" t="n">
-        <v>44.38</v>
+        <v>128.34</v>
       </c>
       <c r="H376">
         <f>הגדרות!B8</f>
@@ -20505,165 +20505,6 @@
       </c>
       <c r="L376">
         <f>I376*(1+J376/100)+K376</f>
-        <v/>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>פורינה (חנויות)</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>דוגלי בוגר בקר</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>חטיפים</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>12368766</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F377" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="G377" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="H377">
-        <f>הגדרות!B8</f>
-        <v/>
-      </c>
-      <c r="I377">
-        <f>F377*(1-H377/100)*1.18</f>
-        <v/>
-      </c>
-      <c r="J377">
-        <f>הגדרות!C8</f>
-        <v/>
-      </c>
-      <c r="K377">
-        <f>הגדרות!D8</f>
-        <v/>
-      </c>
-      <c r="L377">
-        <f>I377*(1+J377/100)+K377</f>
-        <v/>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>פורינה (חנויות)</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>דוגלי בוגר עוף</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>חטיפים</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>12368676</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F378" t="n">
-        <v>108.76</v>
-      </c>
-      <c r="G378" t="n">
-        <v>128.34</v>
-      </c>
-      <c r="H378">
-        <f>הגדרות!B8</f>
-        <v/>
-      </c>
-      <c r="I378">
-        <f>F378*(1-H378/100)*1.18</f>
-        <v/>
-      </c>
-      <c r="J378">
-        <f>הגדרות!C8</f>
-        <v/>
-      </c>
-      <c r="K378">
-        <f>הגדרות!D8</f>
-        <v/>
-      </c>
-      <c r="L378">
-        <f>I378*(1+J378/100)+K378</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>פורינה (חנויות)</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>דוגלי בוגר בקר</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>חטיפים</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>12368675</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="F379" t="n">
-        <v>108.76</v>
-      </c>
-      <c r="G379" t="n">
-        <v>128.34</v>
-      </c>
-      <c r="H379">
-        <f>הגדרות!B8</f>
-        <v/>
-      </c>
-      <c r="I379">
-        <f>F379*(1-H379/100)*1.18</f>
-        <v/>
-      </c>
-      <c r="J379">
-        <f>הגדרות!C8</f>
-        <v/>
-      </c>
-      <c r="K379">
-        <f>הגדרות!D8</f>
-        <v/>
-      </c>
-      <c r="L379">
-        <f>I379*(1+J379/100)+K379</f>
         <v/>
       </c>
     </row>

--- a/downloads/shop.xlsx
+++ b/downloads/shop.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L376"/>
+  <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16536,37 +16536,37 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>@ סדיניה 35 60X90 יח' TENA BED @</t>
+          <t>חטיף הילס היפואלרגני לכלב 200 גרם</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>33262-1</t>
+          <t>40608557</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F302" t="n">
-        <v>31.36</v>
+        <v>24</v>
       </c>
       <c r="G302" t="n">
-        <v>37</v>
+        <v>28.32</v>
       </c>
       <c r="H302">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I302">
@@ -16574,11 +16574,11 @@
         <v/>
       </c>
       <c r="J302">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K302">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L302">
@@ -16589,37 +16589,37 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ANTIGONE WIPES 19*20 500</t>
+          <t>חטיף ווג'ידנט Medium 15 יחידות, 352 גרם</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>M0002020</t>
+          <t>47307870</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F303" t="n">
-        <v>71.42</v>
+        <v>24</v>
       </c>
       <c r="G303" t="n">
-        <v>84.27</v>
+        <v>28.32</v>
       </c>
       <c r="H303">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I303">
@@ -16627,11 +16627,11 @@
         <v/>
       </c>
       <c r="J303">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K303">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L303">
@@ -16642,37 +16642,37 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ANTIGONE WIPES 20*20 200</t>
+          <t>חטיף פודיס מיני ענני עוף לחתולים, 50 גרם</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>100003</t>
+          <t>48000034</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F304" t="n">
-        <v>30.32</v>
+        <v>3.5</v>
       </c>
       <c r="G304" t="n">
-        <v>35.78</v>
+        <v>4.13</v>
       </c>
       <c r="H304">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I304">
@@ -16680,11 +16680,11 @@
         <v/>
       </c>
       <c r="J304">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K304">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L304">
@@ -16695,37 +16695,37 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>CETRIN 1 LITTER SOL</t>
+          <t>חטיף פודיס מיני ענני ברווז לחתולים, 50 גרם</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>48000035</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F305" t="n">
-        <v>30.84</v>
+        <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>36.39</v>
+        <v>4.13</v>
       </c>
       <c r="H305">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I305">
@@ -16733,11 +16733,11 @@
         <v/>
       </c>
       <c r="J305">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K305">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L305">
@@ -16748,37 +16748,37 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DOUXO S3 CALM MOUSSE 150 ML</t>
+          <t>חטיף פודיס דגיגוני סלמון לחתולים, 50 גרם</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>81-105</t>
+          <t>48000036</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F306" t="n">
-        <v>58.47</v>
+        <v>3.5</v>
       </c>
       <c r="G306" t="n">
-        <v>69</v>
+        <v>4.13</v>
       </c>
       <c r="H306">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I306">
@@ -16786,11 +16786,11 @@
         <v/>
       </c>
       <c r="J306">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K306">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L306">
@@ -16806,17 +16806,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DOUXO S3 PYO MOUSSE 150 ML</t>
+          <t>@ סדיניה 35 60X90 יח' TENA BED @</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>81-101</t>
+          <t>33262-1</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16825,10 +16825,10 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>58.47</v>
+        <v>31.36</v>
       </c>
       <c r="G307" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="H307">
         <f>הגדרות!B6</f>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DOUXO S3 PYO PADS</t>
+          <t>ANTIGONE WIPES 19*20 500</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>81-107</t>
+          <t>M0002020</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16878,10 +16878,10 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>36.44</v>
+        <v>71.42</v>
       </c>
       <c r="G308" t="n">
-        <v>43</v>
+        <v>84.27</v>
       </c>
       <c r="H308">
         <f>הגדרות!B6</f>
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DOUXO S3 SEB MOUSSE 150 ML</t>
+          <t>ANTIGONE WIPES 20*20 200</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>81-103</t>
+          <t>100003</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>58.47</v>
+        <v>30.32</v>
       </c>
       <c r="G309" t="n">
-        <v>69</v>
+        <v>35.78</v>
       </c>
       <c r="H309">
         <f>הגדרות!B6</f>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Easy Go 500 Litter - איזי גו</t>
+          <t>CETRIN 1 LITTER SOL</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>18033-1</t>
+          <t>33365</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16984,10 +16984,10 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>14.32</v>
+        <v>30.84</v>
       </c>
       <c r="G310" t="n">
-        <v>16.9</v>
+        <v>36.39</v>
       </c>
       <c r="H310">
         <f>הגדרות!B6</f>
@@ -17018,17 +17018,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Pinchers 45chews peanut butter pill hiding treat</t>
+          <t>DOUXO S3 CALM MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>090062J.045</t>
+          <t>81-105</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17037,10 +17037,10 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>22.3</v>
+        <v>58.47</v>
       </c>
       <c r="G311" t="n">
-        <v>26.31</v>
+        <v>69</v>
       </c>
       <c r="H311">
         <f>הגדרות!B6</f>
@@ -17071,17 +17071,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>אלונקה רכה מתקפלת NAR QuikLitter</t>
+          <t>DOUXO S3 PYO MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>81-101</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>194.49</v>
+        <v>58.47</v>
       </c>
       <c r="G312" t="n">
-        <v>229.5</v>
+        <v>69</v>
       </c>
       <c r="H312">
         <f>הגדרות!B6</f>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>כלוב נשיאה אטלס 10 ללא מזרון Ferplast</t>
+          <t>DOUXO S3 PYO PADS</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>5550279</t>
+          <t>81-107</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17143,10 +17143,10 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>50.85</v>
+        <v>36.44</v>
       </c>
       <c r="G313" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H313">
         <f>הגדרות!B6</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>כלוב נשיאה אטלס 20 ללא מזרון Ferplast</t>
+          <t>DOUXO S3 SEB MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>5550280</t>
+          <t>81-103</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -17196,10 +17196,10 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>88.14</v>
+        <v>58.47</v>
       </c>
       <c r="G314" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="H314">
         <f>הגדרות!B6</f>
@@ -17230,17 +17230,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>מברשת רחצת ידיים לפני ניתוח, סטר', מדיקפרו</t>
+          <t>Easy Go 500 Litter - איזי גו</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>18033-1</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>0.87</v>
+        <v>14.32</v>
       </c>
       <c r="G315" t="n">
-        <v>1.03</v>
+        <v>16.9</v>
       </c>
       <c r="H315">
         <f>הגדרות!B6</f>
@@ -17283,17 +17283,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell sporicidal wipesn 1/6</t>
+          <t>Pinchers 45chews peanut butter pill hiding treat</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>CS25</t>
+          <t>090062J.045</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -17302,10 +17302,10 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>156.78</v>
+        <v>22.3</v>
       </c>
       <c r="G316" t="n">
-        <v>185</v>
+        <v>26.31</v>
       </c>
       <c r="H316">
         <f>הגדרות!B6</f>
@@ -17336,17 +17336,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell Universal wipes clip pack 50</t>
+          <t>אלונקה רכה מתקפלת NAR QuikLitter</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>9.25</v>
+        <v>194.49</v>
       </c>
       <c r="G317" t="n">
-        <v>10.92</v>
+        <v>229.5</v>
       </c>
       <c r="H317">
         <f>הגדרות!B6</f>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell Universal Wipes pack of 200</t>
+          <t>כלוב נשיאה אטלס 10 ללא מזרון Ferplast</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>5550279</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>19.92</v>
+        <v>50.85</v>
       </c>
       <c r="G318" t="n">
-        <v>23.5</v>
+        <v>60</v>
       </c>
       <c r="H318">
         <f>הגדרות!B6</f>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>מגבונים מדי-קלין אקסטרה עבים מועשר באלוורה 500 יח 20X16 ס"מ</t>
+          <t>כלוב נשיאה אטלס 20 ללא מזרון Ferplast</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -17452,7 +17452,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>5550280</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -17461,10 +17461,10 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>22.88</v>
+        <v>88.14</v>
       </c>
       <c r="G319" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="H319">
         <f>הגדרות!B6</f>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>מגבונים מדי-קלין מועשרים באלוורה 500 יח' 28X20 ס"מ</t>
+          <t>מברשת רחצת ידיים לפני ניתוח, סטר', מדיקפרו</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>128695</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>22.88</v>
+        <v>0.87</v>
       </c>
       <c r="G320" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="H320">
         <f>הגדרות!B6</f>
@@ -17548,17 +17548,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>מיטה חשמלית דגם GUESS 402 מעקה מגלוון</t>
+          <t>מגבונים - Clinell sporicidal wipesn 1/6</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>883135</t>
+          <t>CS25</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -17567,10 +17567,10 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>6288.14</v>
+        <v>156.78</v>
       </c>
       <c r="G321" t="n">
-        <v>7420</v>
+        <v>185</v>
       </c>
       <c r="H321">
         <f>הגדרות!B6</f>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>מספריים אל חלד לציפורניים REISZ</t>
+          <t>מגבונים - Clinell Universal wipes clip pack 50</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>434457</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>21.17</v>
+        <v>9.25</v>
       </c>
       <c r="G322" t="n">
-        <v>24.98</v>
+        <v>10.92</v>
       </c>
       <c r="H322">
         <f>הגדרות!B6</f>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>משושת ג'ל 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
+          <t>מגבונים - Clinell Universal Wipes pack of 200</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>67-105</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -17673,10 +17673,10 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>157.63</v>
+        <v>19.92</v>
       </c>
       <c r="G323" t="n">
-        <v>186</v>
+        <v>23.5</v>
       </c>
       <c r="H323">
         <f>הגדרות!B6</f>
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>משושת קרם 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
+          <t>מגבונים מדי-קלין אקסטרה עבים מועשר באלוורה 500 יח 20X16 ס"מ</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>67-103</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>157.63</v>
+        <v>22.88</v>
       </c>
       <c r="G324" t="n">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="H324">
         <f>הגדרות!B6</f>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>נייר לניגוב עדשות מיקרוסקופ 1159 1/280 Kimwipes</t>
+          <t>מגבונים מדי-קלין מועשרים באלוורה 500 יח' 28X20 ס"מ</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -17779,10 +17779,10 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>26.44</v>
+        <v>22.88</v>
       </c>
       <c r="G325" t="n">
-        <v>31.2</v>
+        <v>27</v>
       </c>
       <c r="H325">
         <f>הגדרות!B6</f>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>סיר לילה פלסטיק/ מיטה גדול עם ידית, מדיקפרו</t>
+          <t>מיטה חשמלית דגם GUESS 402 מעקה מגלוון</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>883135</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -17832,10 +17832,10 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>11.86</v>
+        <v>6288.14</v>
       </c>
       <c r="G326" t="n">
-        <v>14</v>
+        <v>7420</v>
       </c>
       <c r="H326">
         <f>הגדרות!B6</f>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>קוצץ ציפורניים, מדיקפרו</t>
+          <t>מספריים אל חלד לציפורניים REISZ</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>434457</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -17885,10 +17885,10 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>3.32</v>
+        <v>21.17</v>
       </c>
       <c r="G327" t="n">
-        <v>3.92</v>
+        <v>24.98</v>
       </c>
       <c r="H327">
         <f>הגדרות!B6</f>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ראש למכונת תספורת (סכין) 40 - 0.25 מ"מ LAUBE</t>
+          <t>משושת ג'ל 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>67-105</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17938,10 +17938,10 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>120.13</v>
+        <v>157.63</v>
       </c>
       <c r="G328" t="n">
-        <v>141.75</v>
+        <v>186</v>
       </c>
       <c r="H328">
         <f>הגדרות!B6</f>
@@ -17972,17 +17972,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>רצועה ללוח גב צבע כתום עם אבזם מתכת</t>
+          <t>משושת קרם 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>67-103</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -17991,10 +17991,10 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>71.19</v>
+        <v>157.63</v>
       </c>
       <c r="G329" t="n">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="H329">
         <f>הגדרות!B6</f>
@@ -18025,17 +18025,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי L</t>
+          <t>נייר לניגוב עדשות מיקרוסקופ 1159 1/280 Kimwipes</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18044,10 +18044,10 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>5.91</v>
+        <v>26.44</v>
       </c>
       <c r="G330" t="n">
-        <v>6.97</v>
+        <v>31.2</v>
       </c>
       <c r="H330">
         <f>הגדרות!B6</f>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי M</t>
+          <t>סיר לילה פלסטיק/ מיטה גדול עם ידית, מדיקפרו</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18097,10 +18097,10 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>6.19</v>
+        <v>11.86</v>
       </c>
       <c r="G331" t="n">
-        <v>7.3</v>
+        <v>14</v>
       </c>
       <c r="H331">
         <f>הגדרות!B6</f>
@@ -18131,17 +18131,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי XL</t>
+          <t>קוצץ ציפורניים, מדיקפרו</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -18150,10 +18150,10 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>6.36</v>
+        <v>3.32</v>
       </c>
       <c r="G332" t="n">
-        <v>7.5</v>
+        <v>3.92</v>
       </c>
       <c r="H332">
         <f>הגדרות!B6</f>
@@ -18179,12 +18179,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Keto Tris Finger Wipes 50 units</t>
+          <t>ראש למכונת תספורת (סכין) 40 - 0.25 מ"מ LAUBE</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -18194,22 +18194,22 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>DERMA-SP1330</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>59</v>
+        <v>120.13</v>
       </c>
       <c r="G333" t="n">
-        <v>69.62</v>
+        <v>141.75</v>
       </c>
       <c r="H333">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I333">
@@ -18217,11 +18217,11 @@
         <v/>
       </c>
       <c r="J333">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K333">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L333">
@@ -18232,37 +18232,37 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tris Ophto Wipes 50ct</t>
+          <t>רצועה ללוח גב צבע כתום עם אבזם מתכת</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>DZOO-TWX</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>58</v>
+        <v>71.19</v>
       </c>
       <c r="G334" t="n">
-        <v>68.44</v>
+        <v>84</v>
       </c>
       <c r="H334">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I334">
@@ -18270,11 +18270,11 @@
         <v/>
       </c>
       <c r="J334">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K334">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L334">
@@ -18285,37 +18285,37 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Pill Splitter</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי L</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>FIONA-821070-1</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>7</v>
+        <v>5.91</v>
       </c>
       <c r="G335" t="n">
-        <v>8.26</v>
+        <v>6.97</v>
       </c>
       <c r="H335">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I335">
@@ -18323,11 +18323,11 @@
         <v/>
       </c>
       <c r="J335">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K335">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L335">
@@ -18338,37 +18338,37 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Calming Spray 200ml</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי M</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>PR-79583</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>46</v>
+        <v>6.19</v>
       </c>
       <c r="G336" t="n">
-        <v>54.28</v>
+        <v>7.3</v>
       </c>
       <c r="H336">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I336">
@@ -18376,11 +18376,11 @@
         <v/>
       </c>
       <c r="J336">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K336">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L336">
@@ -18391,37 +18391,37 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mini Calming Spray 15ml</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי XL</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>PR-79664</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F337" t="n">
-        <v>18</v>
+        <v>6.36</v>
       </c>
       <c r="G337" t="n">
-        <v>21.24</v>
+        <v>7.5</v>
       </c>
       <c r="H337">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I337">
@@ -18429,11 +18429,11 @@
         <v/>
       </c>
       <c r="J337">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K337">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L337">
@@ -18449,17 +18449,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Battery Atomizer Refill 300ml</t>
+          <t>Keto Tris Finger Wipes 50 units</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>PR-79744</t>
+          <t>DERMA-SP1330</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -18468,10 +18468,10 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G338" t="n">
-        <v>66.08</v>
+        <v>69.62</v>
       </c>
       <c r="H338">
         <f>הגדרות!B7</f>
@@ -18502,17 +18502,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Battery Atomizer</t>
+          <t>Tris Ophto Wipes 50ct</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>PR-79745</t>
+          <t>DZOO-TWX</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -18521,10 +18521,10 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="G339" t="n">
-        <v>218.3</v>
+        <v>68.44</v>
       </c>
       <c r="H339">
         <f>הגדרות!B7</f>
@@ -18555,17 +18555,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Calming Wipe Sachet (12)</t>
+          <t>Pill Splitter</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>PR-79881</t>
+          <t>FIONA-821070-1</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -18574,10 +18574,10 @@
         </is>
       </c>
       <c r="F340" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G340" t="n">
-        <v>21.24</v>
+        <v>8.26</v>
       </c>
       <c r="H340">
         <f>הגדרות!B7</f>
@@ -18608,17 +18608,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Boredom Buster forager kit</t>
+          <t>Calming Spray 200ml</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>צעצועים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>PR-80128</t>
+          <t>PR-79583</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -18627,10 +18627,10 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="G341" t="n">
-        <v>123.9</v>
+        <v>54.28</v>
       </c>
       <c r="H341">
         <f>הגדרות!B7</f>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit EXTRA SMALL</t>
+          <t>Mini Calming Spray 15ml</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>PR-79959</t>
+          <t>PR-79664</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -18680,10 +18680,10 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G342" t="n">
-        <v>51.92</v>
+        <v>21.24</v>
       </c>
       <c r="H342">
         <f>הגדרות!B7</f>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit SMALL</t>
+          <t>Battery Atomizer Refill 300ml</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>PR-79960</t>
+          <t>PR-79744</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -18733,10 +18733,10 @@
         </is>
       </c>
       <c r="F343" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G343" t="n">
-        <v>51.92</v>
+        <v>66.08</v>
       </c>
       <c r="H343">
         <f>הגדרות!B7</f>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit MEDIUM</t>
+          <t>Battery Atomizer</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>PR-79961</t>
+          <t>PR-79745</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="F344" t="n">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="G344" t="n">
-        <v>51.92</v>
+        <v>218.3</v>
       </c>
       <c r="H344">
         <f>הגדרות!B7</f>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit LARGE</t>
+          <t>Calming Wipe Sachet (12)</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>PR-79962</t>
+          <t>PR-79881</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -18839,10 +18839,10 @@
         </is>
       </c>
       <c r="F345" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G345" t="n">
-        <v>51.92</v>
+        <v>21.24</v>
       </c>
       <c r="H345">
         <f>הגדרות!B7</f>
@@ -18873,17 +18873,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Calming Spray 400ml – PROF. PACK</t>
+          <t>Boredom Buster forager kit</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>צעצועים</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>PR-79983</t>
+          <t>PR-80128</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -18892,10 +18892,10 @@
         </is>
       </c>
       <c r="F346" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="G346" t="n">
-        <v>71.98</v>
+        <v>123.9</v>
       </c>
       <c r="H346">
         <f>הגדרות!B7</f>
@@ -18921,37 +18921,37 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>Calming Bandana Kit EXTRA SMALL</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>12348261</t>
+          <t>PR-79959</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F347" t="n">
-        <v>8.18</v>
+        <v>44</v>
       </c>
       <c r="G347" t="n">
-        <v>9.65</v>
+        <v>51.92</v>
       </c>
       <c r="H347">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I347">
@@ -18959,11 +18959,11 @@
         <v/>
       </c>
       <c r="J347">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K347">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L347">
@@ -18974,37 +18974,37 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
+          <t>Calming Bandana Kit SMALL</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>12348037</t>
+          <t>PR-79960</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F348" t="n">
-        <v>8.18</v>
+        <v>44</v>
       </c>
       <c r="G348" t="n">
-        <v>9.65</v>
+        <v>51.92</v>
       </c>
       <c r="H348">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I348">
@@ -19012,11 +19012,11 @@
         <v/>
       </c>
       <c r="J348">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K348">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L348">
@@ -19027,37 +19027,37 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
+          <t>Calming Bandana Kit MEDIUM</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>12364507</t>
+          <t>PR-79961</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F349" t="n">
-        <v>8.18</v>
+        <v>44</v>
       </c>
       <c r="G349" t="n">
-        <v>9.65</v>
+        <v>51.92</v>
       </c>
       <c r="H349">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I349">
@@ -19065,11 +19065,11 @@
         <v/>
       </c>
       <c r="J349">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K349">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L349">
@@ -19080,37 +19080,37 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
+          <t>Calming Bandana Kit LARGE</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>12368621</t>
+          <t>PR-79962</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F350" t="n">
-        <v>8.18</v>
+        <v>44</v>
       </c>
       <c r="G350" t="n">
-        <v>9.65</v>
+        <v>51.92</v>
       </c>
       <c r="H350">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I350">
@@ -19118,11 +19118,11 @@
         <v/>
       </c>
       <c r="J350">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K350">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L350">
@@ -19133,37 +19133,37 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
+          <t>Calming Spray 400ml – PROF. PACK</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>12528489</t>
+          <t>PR-79983</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F351" t="n">
-        <v>8.18</v>
+        <v>61</v>
       </c>
       <c r="G351" t="n">
-        <v>9.65</v>
+        <v>71.98</v>
       </c>
       <c r="H351">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I351">
@@ -19171,11 +19171,11 @@
         <v/>
       </c>
       <c r="J351">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K351">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L351">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
+          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>12280472</t>
+          <t>12348261</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס הודו</t>
+          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>12332654</t>
+          <t>12348037</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס עוף</t>
+          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>12332617</t>
+          <t>12364507</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
+          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>12534203</t>
+          <t>12368621</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס עוף וכבד</t>
+          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>12534194</t>
+          <t>12528489</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
+          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>12364794</t>
+          <t>12280472</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>50.67</v>
+        <v>8.18</v>
       </c>
       <c r="G357" t="n">
-        <v>59.79</v>
+        <v>9.65</v>
       </c>
       <c r="H357">
         <f>הגדרות!B8</f>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>פריסקיז פארטי מיקס הודו</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>12349730</t>
+          <t>12332654</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19528,10 +19528,10 @@
         </is>
       </c>
       <c r="F358" t="n">
-        <v>50.67</v>
+        <v>8.18</v>
       </c>
       <c r="G358" t="n">
-        <v>59.79</v>
+        <v>9.65</v>
       </c>
       <c r="H358">
         <f>הגדרות!B8</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע קטן</t>
+          <t>פריסקיז פארטי מיקס עוף</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>12606950</t>
+          <t>12332617</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19581,10 +19581,10 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>10.2</v>
+        <v>8.18</v>
       </c>
       <c r="G359" t="n">
-        <v>12.04</v>
+        <v>9.65</v>
       </c>
       <c r="H359">
         <f>הגדרות!B8</f>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע בינוני</t>
+          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>12606926</t>
+          <t>12534203</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -19634,10 +19634,10 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>10.2</v>
+        <v>8.18</v>
       </c>
       <c r="G360" t="n">
-        <v>12.04</v>
+        <v>9.65</v>
       </c>
       <c r="H360">
         <f>הגדרות!B8</f>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע גדול</t>
+          <t>פריסקיז פלייפולס עוף וכבד</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>12606948</t>
+          <t>12534194</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>10.2</v>
+        <v>8.18</v>
       </c>
       <c r="G361" t="n">
-        <v>12.04</v>
+        <v>9.65</v>
       </c>
       <c r="H361">
         <f>הגדרות!B8</f>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>דנטלייף חתול עוף</t>
+          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>12607325</t>
+          <t>12364794</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -19740,10 +19740,10 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>6.5</v>
+        <v>50.67</v>
       </c>
       <c r="G362" t="n">
-        <v>7.67</v>
+        <v>59.79</v>
       </c>
       <c r="H362">
         <f>הגדרות!B8</f>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>דנטלייף חתול סלמון</t>
+          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>12607342</t>
+          <t>12349730</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -19793,10 +19793,10 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>6.5</v>
+        <v>50.67</v>
       </c>
       <c r="G363" t="n">
-        <v>7.67</v>
+        <v>59.79</v>
       </c>
       <c r="H363">
         <f>הגדרות!B8</f>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables עוף</t>
+          <t>דנטלייף לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>12620437</t>
+          <t>12606950</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -19846,10 +19846,10 @@
         </is>
       </c>
       <c r="F364" t="n">
-        <v>8.49</v>
+        <v>10.2</v>
       </c>
       <c r="G364" t="n">
-        <v>10.02</v>
+        <v>12.04</v>
       </c>
       <c r="H364">
         <f>הגדרות!B8</f>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables סלמון</t>
+          <t>דנטלייף לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>12620438</t>
+          <t>12606926</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19899,10 +19899,10 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>8.49</v>
+        <v>10.2</v>
       </c>
       <c r="G365" t="n">
-        <v>10.02</v>
+        <v>12.04</v>
       </c>
       <c r="H365">
         <f>הגדרות!B8</f>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables ברווז</t>
+          <t>דנטלייף לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>12620419</t>
+          <t>12606948</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>8.49</v>
+        <v>10.2</v>
       </c>
       <c r="G366" t="n">
-        <v>10.02</v>
+        <v>12.04</v>
       </c>
       <c r="H366">
         <f>הגדרות!B8</f>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
+          <t>דנטלייף חתול עוף</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>12604543</t>
+          <t>12607325</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -20005,10 +20005,10 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>25.64</v>
+        <v>6.5</v>
       </c>
       <c r="G367" t="n">
-        <v>30.26</v>
+        <v>7.67</v>
       </c>
       <c r="H367">
         <f>הגדרות!B8</f>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
+          <t>דנטלייף חתול סלמון</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>12604772</t>
+          <t>12607342</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -20058,10 +20058,10 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>25.64</v>
+        <v>6.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.26</v>
+        <v>7.67</v>
       </c>
       <c r="H368">
         <f>הגדרות!B8</f>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
+          <t>פליקס שלוקים Joyables עוף</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>12604733</t>
+          <t>12620437</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -20111,10 +20111,10 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>25.64</v>
+        <v>8.49</v>
       </c>
       <c r="G369" t="n">
-        <v>30.26</v>
+        <v>10.02</v>
       </c>
       <c r="H369">
         <f>הגדרות!B8</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>דוגלי אקטיב בקר</t>
+          <t>פליקס שלוקים Joyables סלמון</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>12466720</t>
+          <t>12620438</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>114.19</v>
+        <v>8.49</v>
       </c>
       <c r="G370" t="n">
-        <v>134.74</v>
+        <v>10.02</v>
       </c>
       <c r="H370">
         <f>הגדרות!B8</f>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>דוגלי גורים עוף</t>
+          <t>פליקס שלוקים Joyables ברווז</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>12466622</t>
+          <t>12620419</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -20217,10 +20217,10 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>41.46</v>
+        <v>8.49</v>
       </c>
       <c r="G371" t="n">
-        <v>48.92</v>
+        <v>10.02</v>
       </c>
       <c r="H371">
         <f>הגדרות!B8</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>דוגלי גזע קטן בקר</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>12613172</t>
+          <t>12604543</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -20270,10 +20270,10 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>39.49</v>
+        <v>25.64</v>
       </c>
       <c r="G372" t="n">
-        <v>46.6</v>
+        <v>30.26</v>
       </c>
       <c r="H372">
         <f>הגדרות!B8</f>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>דוגלי בוגר עוף</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>12368765</t>
+          <t>12604772</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>37.61</v>
+        <v>25.64</v>
       </c>
       <c r="G373" t="n">
-        <v>44.38</v>
+        <v>30.26</v>
       </c>
       <c r="H373">
         <f>הגדרות!B8</f>
@@ -20357,7 +20357,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>דוגלי בוגר בקר</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>12368766</t>
+          <t>12604733</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -20376,10 +20376,10 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>37.61</v>
+        <v>25.64</v>
       </c>
       <c r="G374" t="n">
-        <v>44.38</v>
+        <v>30.26</v>
       </c>
       <c r="H374">
         <f>הגדרות!B8</f>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>דוגלי בוגר עוף</t>
+          <t>דוגלי אקטיב בקר</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>12368676</t>
+          <t>12466720</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>108.76</v>
+        <v>114.19</v>
       </c>
       <c r="G375" t="n">
-        <v>128.34</v>
+        <v>134.74</v>
       </c>
       <c r="H375">
         <f>הגדרות!B8</f>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>דוגלי בוגר בקר</t>
+          <t>דוגלי גורים עוף</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>12368675</t>
+          <t>12466622</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -20482,10 +20482,10 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>108.76</v>
+        <v>41.46</v>
       </c>
       <c r="G376" t="n">
-        <v>128.34</v>
+        <v>48.92</v>
       </c>
       <c r="H376">
         <f>הגדרות!B8</f>
@@ -20505,6 +20505,271 @@
       </c>
       <c r="L376">
         <f>I376*(1+J376/100)+K376</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>דוגלי גזע קטן בקר</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>12613172</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="G377" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="H377">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I377">
+        <f>F377*(1-H377/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J377">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K377">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L377">
+        <f>I377*(1+J377/100)+K377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר עוף</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>12368765</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="G378" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="H378">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I378">
+        <f>F378*(1-H378/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J378">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K378">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L378">
+        <f>I378*(1+J378/100)+K378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר בקר</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>12368766</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="G379" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="H379">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I379">
+        <f>F379*(1-H379/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J379">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K379">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L379">
+        <f>I379*(1+J379/100)+K379</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר עוף</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>12368676</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>108.76</v>
+      </c>
+      <c r="G380" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="H380">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I380">
+        <f>F380*(1-H380/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J380">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K380">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L380">
+        <f>I380*(1+J380/100)+K380</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר בקר</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>12368675</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>108.76</v>
+      </c>
+      <c r="G381" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="H381">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I381">
+        <f>F381*(1-H381/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J381">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K381">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L381">
+        <f>I381*(1+J381/100)+K381</f>
         <v/>
       </c>
     </row>

--- a/downloads/shop.xlsx
+++ b/downloads/shop.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16801,37 +16801,37 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>@ סדיניה 35 60X90 יח' TENA BED @</t>
+          <t>חול Kit4Cat</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>33262-1</t>
+          <t>460001</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F307" t="n">
-        <v>31.36</v>
+        <v>40</v>
       </c>
       <c r="G307" t="n">
-        <v>37</v>
+        <v>47.2</v>
       </c>
       <c r="H307">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I307">
@@ -16839,11 +16839,11 @@
         <v/>
       </c>
       <c r="J307">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K307">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L307">
@@ -16854,37 +16854,37 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ANTIGONE WIPES 19*20 500</t>
+          <t>חטיף ווג'ידנט 15 Small יחידות, 228 גרם</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>M0002020</t>
+          <t>47307869</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F308" t="n">
-        <v>71.42</v>
+        <v>19</v>
       </c>
       <c r="G308" t="n">
-        <v>84.27</v>
+        <v>22.42</v>
       </c>
       <c r="H308">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I308">
@@ -16892,11 +16892,11 @@
         <v/>
       </c>
       <c r="J308">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K308">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L308">
@@ -16907,37 +16907,37 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>מדי-מרקט</t>
+          <t>וטמרקט</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ANTIGONE WIPES 20*20 200</t>
+          <t>חטיף ווג'ידנט 15 Large יחידות, 502 גרם</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>100003</t>
+          <t>47307871</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>30.32</v>
+        <v>30</v>
       </c>
       <c r="G309" t="n">
-        <v>35.78</v>
+        <v>35.4</v>
       </c>
       <c r="H309">
-        <f>הגדרות!B6</f>
+        <f>הגדרות!B5</f>
         <v/>
       </c>
       <c r="I309">
@@ -16945,11 +16945,11 @@
         <v/>
       </c>
       <c r="J309">
-        <f>הגדרות!C6</f>
+        <f>הגדרות!C5</f>
         <v/>
       </c>
       <c r="K309">
-        <f>הגדרות!D6</f>
+        <f>הגדרות!D5</f>
         <v/>
       </c>
       <c r="L309">
@@ -16965,17 +16965,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CETRIN 1 LITTER SOL</t>
+          <t>@ סדיניה 35 60X90 יח' TENA BED @</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>33262-1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16984,10 +16984,10 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>30.84</v>
+        <v>31.36</v>
       </c>
       <c r="G310" t="n">
-        <v>36.39</v>
+        <v>37</v>
       </c>
       <c r="H310">
         <f>הגדרות!B6</f>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DOUXO S3 CALM MOUSSE 150 ML</t>
+          <t>ANTIGONE WIPES 19*20 500</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>81-105</t>
+          <t>M0002020</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17037,10 +17037,10 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>58.47</v>
+        <v>71.42</v>
       </c>
       <c r="G311" t="n">
-        <v>69</v>
+        <v>84.27</v>
       </c>
       <c r="H311">
         <f>הגדרות!B6</f>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DOUXO S3 PYO MOUSSE 150 ML</t>
+          <t>ANTIGONE WIPES 20*20 200</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>81-101</t>
+          <t>100003</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>58.47</v>
+        <v>30.32</v>
       </c>
       <c r="G312" t="n">
-        <v>69</v>
+        <v>35.78</v>
       </c>
       <c r="H312">
         <f>הגדרות!B6</f>
@@ -17124,17 +17124,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DOUXO S3 PYO PADS</t>
+          <t>CETRIN 1 LITTER SOL</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>81-107</t>
+          <t>33365</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17143,10 +17143,10 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>36.44</v>
+        <v>30.84</v>
       </c>
       <c r="G313" t="n">
-        <v>43</v>
+        <v>36.39</v>
       </c>
       <c r="H313">
         <f>הגדרות!B6</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DOUXO S3 SEB MOUSSE 150 ML</t>
+          <t>DOUXO S3 CALM MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>81-103</t>
+          <t>81-105</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -17230,17 +17230,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Easy Go 500 Litter - איזי גו</t>
+          <t>DOUXO S3 PYO MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>18033-1</t>
+          <t>81-101</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>14.32</v>
+        <v>58.47</v>
       </c>
       <c r="G315" t="n">
-        <v>16.9</v>
+        <v>69</v>
       </c>
       <c r="H315">
         <f>הגדרות!B6</f>
@@ -17283,17 +17283,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Pinchers 45chews peanut butter pill hiding treat</t>
+          <t>DOUXO S3 PYO PADS</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>090062J.045</t>
+          <t>81-107</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -17302,10 +17302,10 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>22.3</v>
+        <v>36.44</v>
       </c>
       <c r="G316" t="n">
-        <v>26.31</v>
+        <v>43</v>
       </c>
       <c r="H316">
         <f>הגדרות!B6</f>
@@ -17336,17 +17336,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>אלונקה רכה מתקפלת NAR QuikLitter</t>
+          <t>DOUXO S3 SEB MOUSSE 150 ML</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>81-103</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>194.49</v>
+        <v>58.47</v>
       </c>
       <c r="G317" t="n">
-        <v>229.5</v>
+        <v>69</v>
       </c>
       <c r="H317">
         <f>הגדרות!B6</f>
@@ -17389,17 +17389,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>כלוב נשיאה אטלס 10 ללא מזרון Ferplast</t>
+          <t>Easy Go 500 Litter - איזי גו</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>5550279</t>
+          <t>18033-1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>50.85</v>
+        <v>14.32</v>
       </c>
       <c r="G318" t="n">
-        <v>60</v>
+        <v>16.9</v>
       </c>
       <c r="H318">
         <f>הגדרות!B6</f>
@@ -17442,17 +17442,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>כלוב נשיאה אטלס 20 ללא מזרון Ferplast</t>
+          <t>Pinchers 45chews peanut butter pill hiding treat</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חטיפים</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>5550280</t>
+          <t>090062J.045</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -17461,10 +17461,10 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>88.14</v>
+        <v>22.3</v>
       </c>
       <c r="G319" t="n">
-        <v>104</v>
+        <v>26.31</v>
       </c>
       <c r="H319">
         <f>הגדרות!B6</f>
@@ -17495,17 +17495,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>מברשת רחצת ידיים לפני ניתוח, סטר', מדיקפרו</t>
+          <t>אלונקה רכה מתקפלת NAR QuikLitter</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>0.87</v>
+        <v>194.49</v>
       </c>
       <c r="G320" t="n">
-        <v>1.03</v>
+        <v>229.5</v>
       </c>
       <c r="H320">
         <f>הגדרות!B6</f>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell sporicidal wipesn 1/6</t>
+          <t>כלוב נשיאה אטלס 10 ללא מזרון Ferplast</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>CS25</t>
+          <t>5550279</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -17567,10 +17567,10 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>156.78</v>
+        <v>50.85</v>
       </c>
       <c r="G321" t="n">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="H321">
         <f>הגדרות!B6</f>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell Universal wipes clip pack 50</t>
+          <t>כלוב נשיאה אטלס 20 ללא מזרון Ferplast</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>5550280</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>9.25</v>
+        <v>88.14</v>
       </c>
       <c r="G322" t="n">
-        <v>10.92</v>
+        <v>104</v>
       </c>
       <c r="H322">
         <f>הגדרות!B6</f>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>מגבונים - Clinell Universal Wipes pack of 200</t>
+          <t>מברשת רחצת ידיים לפני ניתוח, סטר', מדיקפרו</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -17673,10 +17673,10 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>19.92</v>
+        <v>0.87</v>
       </c>
       <c r="G323" t="n">
-        <v>23.5</v>
+        <v>1.03</v>
       </c>
       <c r="H323">
         <f>הגדרות!B6</f>
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>מגבונים מדי-קלין אקסטרה עבים מועשר באלוורה 500 יח 20X16 ס"מ</t>
+          <t>מגבונים - Clinell sporicidal wipesn 1/6</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>CS25</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>22.88</v>
+        <v>156.78</v>
       </c>
       <c r="G324" t="n">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H324">
         <f>הגדרות!B6</f>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>מגבונים מדי-קלין מועשרים באלוורה 500 יח' 28X20 ס"מ</t>
+          <t>מגבונים - Clinell Universal wipes clip pack 50</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>128695</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -17779,10 +17779,10 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>22.88</v>
+        <v>9.25</v>
       </c>
       <c r="G325" t="n">
-        <v>27</v>
+        <v>10.92</v>
       </c>
       <c r="H325">
         <f>הגדרות!B6</f>
@@ -17813,17 +17813,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>מיטה חשמלית דגם GUESS 402 מעקה מגלוון</t>
+          <t>מגבונים - Clinell Universal Wipes pack of 200</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>883135</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -17832,10 +17832,10 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>6288.14</v>
+        <v>19.92</v>
       </c>
       <c r="G326" t="n">
-        <v>7420</v>
+        <v>23.5</v>
       </c>
       <c r="H326">
         <f>הגדרות!B6</f>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>מספריים אל חלד לציפורניים REISZ</t>
+          <t>מגבונים מדי-קלין אקסטרה עבים מועשר באלוורה 500 יח 20X16 ס"מ</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>434457</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -17885,10 +17885,10 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>21.17</v>
+        <v>22.88</v>
       </c>
       <c r="G327" t="n">
-        <v>24.98</v>
+        <v>27</v>
       </c>
       <c r="H327">
         <f>הגדרות!B6</f>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>משושת ג'ל 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
+          <t>מגבונים מדי-קלין מועשרים באלוורה 500 יח' 28X20 ס"מ</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>67-105</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17938,10 +17938,10 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>157.63</v>
+        <v>22.88</v>
       </c>
       <c r="G328" t="n">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="H328">
         <f>הגדרות!B6</f>
@@ -17972,17 +17972,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>משושת קרם 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
+          <t>מיטה חשמלית דגם GUESS 402 מעקה מגלוון</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>67-103</t>
+          <t>883135</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -17991,10 +17991,10 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>157.63</v>
+        <v>6288.14</v>
       </c>
       <c r="G329" t="n">
-        <v>186</v>
+        <v>7420</v>
       </c>
       <c r="H329">
         <f>הגדרות!B6</f>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>נייר לניגוב עדשות מיקרוסקופ 1159 1/280 Kimwipes</t>
+          <t>מספריים אל חלד לציפורניים REISZ</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>434457</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18044,10 +18044,10 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>26.44</v>
+        <v>21.17</v>
       </c>
       <c r="G330" t="n">
-        <v>31.2</v>
+        <v>24.98</v>
       </c>
       <c r="H330">
         <f>הגדרות!B6</f>
@@ -18078,17 +18078,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>סיר לילה פלסטיק/ מיטה גדול עם ידית, מדיקפרו</t>
+          <t>משושת ג'ל 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>67-105</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18097,10 +18097,10 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>11.86</v>
+        <v>157.63</v>
       </c>
       <c r="G331" t="n">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="H331">
         <f>הגדרות!B6</f>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>קוצץ ציפורניים, מדיקפרו</t>
+          <t>משושת קרם 500 מ"ל פוליגונום רב תכליתי Herbaderm</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>67-103</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -18150,10 +18150,10 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3.32</v>
+        <v>157.63</v>
       </c>
       <c r="G332" t="n">
-        <v>3.92</v>
+        <v>186</v>
       </c>
       <c r="H332">
         <f>הגדרות!B6</f>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ראש למכונת תספורת (סכין) 40 - 0.25 מ"מ LAUBE</t>
+          <t>נייר לניגוב עדשות מיקרוסקופ 1159 1/280 Kimwipes</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -18203,10 +18203,10 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>120.13</v>
+        <v>26.44</v>
       </c>
       <c r="G333" t="n">
-        <v>141.75</v>
+        <v>31.2</v>
       </c>
       <c r="H333">
         <f>הגדרות!B6</f>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>רצועה ללוח גב צבע כתום עם אבזם מתכת</t>
+          <t>סיר לילה פלסטיק/ מיטה גדול עם ידית, מדיקפרו</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -18256,10 +18256,10 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>71.19</v>
+        <v>11.86</v>
       </c>
       <c r="G334" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="H334">
         <f>הגדרות!B6</f>
@@ -18290,17 +18290,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי L</t>
+          <t>קוצץ ציפורניים, מדיקפרו</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>5.91</v>
+        <v>3.32</v>
       </c>
       <c r="G335" t="n">
-        <v>6.97</v>
+        <v>3.92</v>
       </c>
       <c r="H335">
         <f>הגדרות!B6</f>
@@ -18343,17 +18343,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי M</t>
+          <t>ראש למכונת תספורת (סכין) 40 - 0.25 מ"מ LAUBE</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>אביזרים</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -18362,10 +18362,10 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>6.19</v>
+        <v>120.13</v>
       </c>
       <c r="G336" t="n">
-        <v>7.3</v>
+        <v>141.75</v>
       </c>
       <c r="H336">
         <f>הגדרות!B6</f>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>רצועה לתמיכה למסכת טרכוסטומי XL</t>
+          <t>רצועה ללוח גב צבע כתום עם אבזם מתכת</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -18415,10 +18415,10 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>6.36</v>
+        <v>71.19</v>
       </c>
       <c r="G337" t="n">
-        <v>7.5</v>
+        <v>84</v>
       </c>
       <c r="H337">
         <f>הגדרות!B6</f>
@@ -18444,37 +18444,37 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Keto Tris Finger Wipes 50 units</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי L</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>DERMA-SP1330</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F338" t="n">
-        <v>59</v>
+        <v>5.91</v>
       </c>
       <c r="G338" t="n">
-        <v>69.62</v>
+        <v>6.97</v>
       </c>
       <c r="H338">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I338">
@@ -18482,11 +18482,11 @@
         <v/>
       </c>
       <c r="J338">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K338">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L338">
@@ -18497,37 +18497,37 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tris Ophto Wipes 50ct</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי M</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>טיפוח והיגיינה</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>DZOO-TWX</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F339" t="n">
-        <v>58</v>
+        <v>6.19</v>
       </c>
       <c r="G339" t="n">
-        <v>68.44</v>
+        <v>7.3</v>
       </c>
       <c r="H339">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I339">
@@ -18535,11 +18535,11 @@
         <v/>
       </c>
       <c r="J339">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K339">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L339">
@@ -18550,37 +18550,37 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>פט-וט ביומד</t>
+          <t>מדי-מרקט</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Pill Splitter</t>
+          <t>רצועה לתמיכה למסכת טרכוסטומי XL</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>חול ושירותים</t>
+          <t>אביזרים</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>FIONA-821070-1</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>7</v>
+        <v>6.36</v>
       </c>
       <c r="G340" t="n">
-        <v>8.26</v>
+        <v>7.5</v>
       </c>
       <c r="H340">
-        <f>הגדרות!B7</f>
+        <f>הגדרות!B6</f>
         <v/>
       </c>
       <c r="I340">
@@ -18588,11 +18588,11 @@
         <v/>
       </c>
       <c r="J340">
-        <f>הגדרות!C7</f>
+        <f>הגדרות!C6</f>
         <v/>
       </c>
       <c r="K340">
-        <f>הגדרות!D7</f>
+        <f>הגדרות!D6</f>
         <v/>
       </c>
       <c r="L340">
@@ -18608,17 +18608,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Calming Spray 200ml</t>
+          <t>Keto Tris Finger Wipes 50 units</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>PR-79583</t>
+          <t>DERMA-SP1330</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -18627,10 +18627,10 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G341" t="n">
-        <v>54.28</v>
+        <v>69.62</v>
       </c>
       <c r="H341">
         <f>הגדרות!B7</f>
@@ -18661,17 +18661,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mini Calming Spray 15ml</t>
+          <t>Tris Ophto Wipes 50ct</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>טיפוח והיגיינה</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>PR-79664</t>
+          <t>DZOO-TWX</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -18680,10 +18680,10 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G342" t="n">
-        <v>21.24</v>
+        <v>68.44</v>
       </c>
       <c r="H342">
         <f>הגדרות!B7</f>
@@ -18714,17 +18714,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Battery Atomizer Refill 300ml</t>
+          <t>Pill Splitter</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>חול ושירותים</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>PR-79744</t>
+          <t>FIONA-821070-1</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -18733,10 +18733,10 @@
         </is>
       </c>
       <c r="F343" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G343" t="n">
-        <v>66.08</v>
+        <v>8.26</v>
       </c>
       <c r="H343">
         <f>הגדרות!B7</f>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Battery Atomizer</t>
+          <t>Calming Spray 200ml</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>PR-79745</t>
+          <t>PR-79583</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="F344" t="n">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="G344" t="n">
-        <v>218.3</v>
+        <v>54.28</v>
       </c>
       <c r="H344">
         <f>הגדרות!B7</f>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Calming Wipe Sachet (12)</t>
+          <t>Mini Calming Spray 15ml</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>PR-79881</t>
+          <t>PR-79664</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -18873,17 +18873,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Boredom Buster forager kit</t>
+          <t>Battery Atomizer Refill 300ml</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>צעצועים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>PR-80128</t>
+          <t>PR-79744</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -18892,10 +18892,10 @@
         </is>
       </c>
       <c r="F346" t="n">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="G346" t="n">
-        <v>123.9</v>
+        <v>66.08</v>
       </c>
       <c r="H346">
         <f>הגדרות!B7</f>
@@ -18926,7 +18926,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit EXTRA SMALL</t>
+          <t>Battery Atomizer</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>PR-79959</t>
+          <t>PR-79745</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -18945,10 +18945,10 @@
         </is>
       </c>
       <c r="F347" t="n">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="G347" t="n">
-        <v>51.92</v>
+        <v>218.3</v>
       </c>
       <c r="H347">
         <f>הגדרות!B7</f>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit SMALL</t>
+          <t>Calming Wipe Sachet (12)</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>PR-79960</t>
+          <t>PR-79881</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -18998,10 +18998,10 @@
         </is>
       </c>
       <c r="F348" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G348" t="n">
-        <v>51.92</v>
+        <v>21.24</v>
       </c>
       <c r="H348">
         <f>הגדרות!B7</f>
@@ -19032,17 +19032,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit MEDIUM</t>
+          <t>Boredom Buster forager kit</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>הרגעה</t>
+          <t>צעצועים</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>PR-79961</t>
+          <t>PR-80128</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -19051,10 +19051,10 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="G349" t="n">
-        <v>51.92</v>
+        <v>123.9</v>
       </c>
       <c r="H349">
         <f>הגדרות!B7</f>
@@ -19085,7 +19085,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Calming Bandana Kit LARGE</t>
+          <t>Calming Bandana Kit EXTRA SMALL</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>PR-79962</t>
+          <t>PR-79959</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Calming Spray 400ml – PROF. PACK</t>
+          <t>Calming Bandana Kit SMALL</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>PR-79983</t>
+          <t>PR-79960</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -19157,10 +19157,10 @@
         </is>
       </c>
       <c r="F351" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="G351" t="n">
-        <v>71.98</v>
+        <v>51.92</v>
       </c>
       <c r="H351">
         <f>הגדרות!B7</f>
@@ -19186,37 +19186,37 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>Calming Bandana Kit MEDIUM</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>12348261</t>
+          <t>PR-79961</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F352" t="n">
-        <v>8.18</v>
+        <v>44</v>
       </c>
       <c r="G352" t="n">
-        <v>9.65</v>
+        <v>51.92</v>
       </c>
       <c r="H352">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I352">
@@ -19224,11 +19224,11 @@
         <v/>
       </c>
       <c r="J352">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K352">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L352">
@@ -19239,37 +19239,37 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
+          <t>Calming Bandana Kit LARGE</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>12348037</t>
+          <t>PR-79962</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>8.18</v>
+        <v>44</v>
       </c>
       <c r="G353" t="n">
-        <v>9.65</v>
+        <v>51.92</v>
       </c>
       <c r="H353">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I353">
@@ -19277,11 +19277,11 @@
         <v/>
       </c>
       <c r="J353">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K353">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L353">
@@ -19292,37 +19292,37 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>פורינה (חנויות)</t>
+          <t>פט-וט ביומד</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
+          <t>Calming Spray 400ml – PROF. PACK</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>חטיפים</t>
+          <t>הרגעה</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>12364507</t>
+          <t>PR-79983</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>8.18</v>
+        <v>61</v>
       </c>
       <c r="G354" t="n">
-        <v>9.65</v>
+        <v>71.98</v>
       </c>
       <c r="H354">
-        <f>הגדרות!B8</f>
+        <f>הגדרות!B7</f>
         <v/>
       </c>
       <c r="I354">
@@ -19330,11 +19330,11 @@
         <v/>
       </c>
       <c r="J354">
-        <f>הגדרות!C8</f>
+        <f>הגדרות!C7</f>
         <v/>
       </c>
       <c r="K354">
-        <f>הגדרות!D8</f>
+        <f>הגדרות!D7</f>
         <v/>
       </c>
       <c r="L354">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
+          <t>פריסקיז פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>12368621</t>
+          <t>12348261</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
+          <t>פריסקיז פארטי מיקס מיקס גריל קראנץ</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>12528489</t>
+          <t>12348037</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
+          <t>פריסקיז פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>12280472</t>
+          <t>12364507</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס הודו</t>
+          <t>פריסקיז פארטי מיקס פיקניק קרנץ</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>12332654</t>
+          <t>12368621</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>פריסקיז פארטי מיקס עוף</t>
+          <t>פריסקיז פארטי מיקס קרייזי צ'יז</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>12332617</t>
+          <t>12528489</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
+          <t>פריסקיז פארטי מיקס מאנץ' בוקר</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>12534203</t>
+          <t>12280472</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>פריסקיז פלייפולס עוף וכבד</t>
+          <t>פריסקיז פארטי מיקס הודו</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>12534194</t>
+          <t>12332654</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
+          <t>פריסקיז פארטי מיקס עוף</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>12364794</t>
+          <t>12332617</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -19740,10 +19740,10 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>50.67</v>
+        <v>8.18</v>
       </c>
       <c r="G362" t="n">
-        <v>59.79</v>
+        <v>9.65</v>
       </c>
       <c r="H362">
         <f>הגדרות!B8</f>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
+          <t>פריסקיז פלייפולס סלמון ושרימפס</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>12349730</t>
+          <t>12534203</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -19793,10 +19793,10 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>50.67</v>
+        <v>8.18</v>
       </c>
       <c r="G363" t="n">
-        <v>59.79</v>
+        <v>9.65</v>
       </c>
       <c r="H363">
         <f>הגדרות!B8</f>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע קטן</t>
+          <t>פריסקיז פלייפולס עוף וכבד</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>12606950</t>
+          <t>12534194</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -19846,10 +19846,10 @@
         </is>
       </c>
       <c r="F364" t="n">
-        <v>10.2</v>
+        <v>8.18</v>
       </c>
       <c r="G364" t="n">
-        <v>12.04</v>
+        <v>9.65</v>
       </c>
       <c r="H364">
         <f>הגדרות!B8</f>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע בינוני</t>
+          <t>פריסקיז צנצנת פארטי מיקס מעדני ים קראנץ</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>12606926</t>
+          <t>12364794</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19899,10 +19899,10 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>10.2</v>
+        <v>50.67</v>
       </c>
       <c r="G365" t="n">
-        <v>12.04</v>
+        <v>59.79</v>
       </c>
       <c r="H365">
         <f>הגדרות!B8</f>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>דנטלייף לכלב מגזע גדול</t>
+          <t>פריסקיז צנצנת פארטי מיקס אוריגי'נל קראנץ</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>12606948</t>
+          <t>12349730</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -19952,10 +19952,10 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>10.2</v>
+        <v>50.67</v>
       </c>
       <c r="G366" t="n">
-        <v>12.04</v>
+        <v>59.79</v>
       </c>
       <c r="H366">
         <f>הגדרות!B8</f>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>דנטלייף חתול עוף</t>
+          <t>דנטלייף לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>12607325</t>
+          <t>12606950</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -20005,10 +20005,10 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>6.5</v>
+        <v>10.2</v>
       </c>
       <c r="G367" t="n">
-        <v>7.67</v>
+        <v>12.04</v>
       </c>
       <c r="H367">
         <f>הגדרות!B8</f>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>דנטלייף חתול סלמון</t>
+          <t>דנטלייף לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>12607342</t>
+          <t>12606926</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -20058,10 +20058,10 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>6.5</v>
+        <v>10.2</v>
       </c>
       <c r="G368" t="n">
-        <v>7.67</v>
+        <v>12.04</v>
       </c>
       <c r="H368">
         <f>הגדרות!B8</f>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables עוף</t>
+          <t>דנטלייף לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>12620437</t>
+          <t>12606948</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -20111,10 +20111,10 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>8.49</v>
+        <v>10.2</v>
       </c>
       <c r="G369" t="n">
-        <v>10.02</v>
+        <v>12.04</v>
       </c>
       <c r="H369">
         <f>הגדרות!B8</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables סלמון</t>
+          <t>דנטלייף חתול עוף</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>12620438</t>
+          <t>12607325</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>8.49</v>
+        <v>6.5</v>
       </c>
       <c r="G370" t="n">
-        <v>10.02</v>
+        <v>7.67</v>
       </c>
       <c r="H370">
         <f>הגדרות!B8</f>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>פליקס שלוקים Joyables ברווז</t>
+          <t>דנטלייף חתול סלמון</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>12620419</t>
+          <t>12607342</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -20217,10 +20217,10 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>8.49</v>
+        <v>6.5</v>
       </c>
       <c r="G371" t="n">
-        <v>10.02</v>
+        <v>7.67</v>
       </c>
       <c r="H371">
         <f>הגדרות!B8</f>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
+          <t>פליקס שלוקים Joyables עוף</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>12604543</t>
+          <t>12620437</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -20270,10 +20270,10 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>25.64</v>
+        <v>8.49</v>
       </c>
       <c r="G372" t="n">
-        <v>30.26</v>
+        <v>10.02</v>
       </c>
       <c r="H372">
         <f>הגדרות!B8</f>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
+          <t>פליקס שלוקים Joyables סלמון</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>12604772</t>
+          <t>12620438</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>25.64</v>
+        <v>8.49</v>
       </c>
       <c r="G373" t="n">
-        <v>30.26</v>
+        <v>10.02</v>
       </c>
       <c r="H373">
         <f>הגדרות!B8</f>
@@ -20357,7 +20357,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
+          <t>פליקס שלוקים Joyables ברווז</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>12604733</t>
+          <t>12620419</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -20376,10 +20376,10 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>25.64</v>
+        <v>8.49</v>
       </c>
       <c r="G374" t="n">
-        <v>30.26</v>
+        <v>10.02</v>
       </c>
       <c r="H374">
         <f>הגדרות!B8</f>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>דוגלי אקטיב בקר</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע קטן</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>12466720</t>
+          <t>12604543</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -20429,10 +20429,10 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>114.19</v>
+        <v>25.64</v>
       </c>
       <c r="G375" t="n">
-        <v>134.74</v>
+        <v>30.26</v>
       </c>
       <c r="H375">
         <f>הגדרות!B8</f>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>דוגלי גורים עוף</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע בינוני</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>12466622</t>
+          <t>12604772</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -20482,10 +20482,10 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>41.46</v>
+        <v>25.64</v>
       </c>
       <c r="G376" t="n">
-        <v>48.92</v>
+        <v>30.26</v>
       </c>
       <c r="H376">
         <f>הגדרות!B8</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>דוגלי גזע קטן בקר</t>
+          <t>פרו פלאן חטיפי DentalCare לכלב מגזע גדול</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>12613172</t>
+          <t>12604733</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -20535,10 +20535,10 @@
         </is>
       </c>
       <c r="F377" t="n">
-        <v>39.49</v>
+        <v>25.64</v>
       </c>
       <c r="G377" t="n">
-        <v>46.6</v>
+        <v>30.26</v>
       </c>
       <c r="H377">
         <f>הגדרות!B8</f>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>דוגלי בוגר עוף</t>
+          <t>דוגלי אקטיב בקר</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>12368765</t>
+          <t>12466720</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -20588,10 +20588,10 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>37.61</v>
+        <v>114.19</v>
       </c>
       <c r="G378" t="n">
-        <v>44.38</v>
+        <v>134.74</v>
       </c>
       <c r="H378">
         <f>הגדרות!B8</f>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>דוגלי בוגר בקר</t>
+          <t>דוגלי גורים עוף</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>12368766</t>
+          <t>12466622</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -20641,10 +20641,10 @@
         </is>
       </c>
       <c r="F379" t="n">
-        <v>37.61</v>
+        <v>41.46</v>
       </c>
       <c r="G379" t="n">
-        <v>44.38</v>
+        <v>48.92</v>
       </c>
       <c r="H379">
         <f>הגדרות!B8</f>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>דוגלי בוגר עוף</t>
+          <t>דוגלי גזע קטן בקר</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -20685,7 +20685,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>12368676</t>
+          <t>12613172</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>108.76</v>
+        <v>39.49</v>
       </c>
       <c r="G380" t="n">
-        <v>128.34</v>
+        <v>46.6</v>
       </c>
       <c r="H380">
         <f>הגדרות!B8</f>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>דוגלי בוגר בקר</t>
+          <t>דוגלי בוגר עוף</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>12368675</t>
+          <t>12368765</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -20747,10 +20747,10 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>108.76</v>
+        <v>37.61</v>
       </c>
       <c r="G381" t="n">
-        <v>128.34</v>
+        <v>44.38</v>
       </c>
       <c r="H381">
         <f>הגדרות!B8</f>
@@ -20770,6 +20770,165 @@
       </c>
       <c r="L381">
         <f>I381*(1+J381/100)+K381</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר בקר</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>12368766</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="G382" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="H382">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I382">
+        <f>F382*(1-H382/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J382">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K382">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L382">
+        <f>I382*(1+J382/100)+K382</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר עוף</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>12368676</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>108.76</v>
+      </c>
+      <c r="G383" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="H383">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I383">
+        <f>F383*(1-H383/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J383">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K383">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L383">
+        <f>I383*(1+J383/100)+K383</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>פורינה (חנויות)</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>דוגלי בוגר בקר</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>חטיפים</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>12368675</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>108.76</v>
+      </c>
+      <c r="G384" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="H384">
+        <f>הגדרות!B8</f>
+        <v/>
+      </c>
+      <c r="I384">
+        <f>F384*(1-H384/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J384">
+        <f>הגדרות!C8</f>
+        <v/>
+      </c>
+      <c r="K384">
+        <f>הגדרות!D8</f>
+        <v/>
+      </c>
+      <c r="L384">
+        <f>I384*(1+J384/100)+K384</f>
         <v/>
       </c>
     </row>
